--- a/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/1_four_bus_radial_1ph_grid_MP_pf_sc_results_1_bus.xlsx
+++ b/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/1_four_bus_radial_1ph_grid_MP_pf_sc_results_1_bus.xlsx
@@ -720,22 +720,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.100539455419024</v>
+        <v>1.100539455419038</v>
       </c>
       <c r="O2">
-        <v>1.097995431674444</v>
+        <v>1.097995431674429</v>
       </c>
       <c r="P2">
-        <v>1.098457996344464</v>
+        <v>1.098457996344437</v>
       </c>
       <c r="Q2">
         <v>29.92348286443664</v>
       </c>
       <c r="R2">
-        <v>-90.12536079167887</v>
+        <v>-90.12536079168052</v>
       </c>
       <c r="S2">
-        <v>150.0140081536936</v>
+        <v>150.014008153694</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -746,55 +746,55 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>0.3557435519611505</v>
+        <v>0.3557435519621827</v>
       </c>
       <c r="D3">
-        <v>0.3557435519611505</v>
+        <v>0.3557435519621827</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.08215545541910921</v>
+        <v>0.0821554554193476</v>
       </c>
       <c r="G3">
-        <v>0.08215545541910924</v>
+        <v>0.08215545541934759</v>
       </c>
       <c r="H3">
-        <v>2.04881092492271</v>
+        <v>2.048810925117779</v>
       </c>
       <c r="I3">
-        <v>1.383392955552335</v>
+        <v>1.383392955720942</v>
       </c>
       <c r="J3">
-        <v>0.5116751132846749</v>
+        <v>0.5116751132619101</v>
       </c>
       <c r="K3">
-        <v>0.3473264055688352</v>
+        <v>0.347326405539256</v>
       </c>
       <c r="L3">
-        <v>0.5116751132846632</v>
+        <v>0.5116751132525802</v>
       </c>
       <c r="M3">
-        <v>0.3473264055688411</v>
+        <v>0.3473264055744294</v>
       </c>
       <c r="N3">
-        <v>0.9526279648105369</v>
+        <v>0.952627964815119</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>0.9526279648105332</v>
+        <v>0.9526279648119598</v>
       </c>
       <c r="Q3">
-        <v>3.516126893381421E-13</v>
+        <v>-1.011115970288249E-10</v>
       </c>
       <c r="R3">
         <v>0</v>
       </c>
       <c r="S3">
-        <v>179.9999999999924</v>
+        <v>-179.9999999993845</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -838,22 +838,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.9526279517434754</v>
+        <v>0.9526279517475256</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.9526279778775952</v>
+        <v>0.9526279778757328</v>
       </c>
       <c r="Q4">
-        <v>1.163269858554002E-06</v>
+        <v>1.163082502386709E-06</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>179.9999988367229</v>
+        <v>179.9999988373277</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -897,22 +897,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9526279569702997</v>
+        <v>0.95262795697431</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0.9526279726507707</v>
+        <v>0.9526279726486904</v>
       </c>
       <c r="Q5">
-        <v>6.979620565742021E-07</v>
+        <v>6.978481674565027E-07</v>
       </c>
       <c r="R5">
         <v>0</v>
       </c>
       <c r="S5">
-        <v>179.9999993020307</v>
+        <v>179.9999993028406</v>
       </c>
     </row>
   </sheetData>
@@ -1028,19 +1028,19 @@
         <v>1.050040203479655</v>
       </c>
       <c r="O2">
-        <v>1.049678265284739</v>
+        <v>1.049678265284738</v>
       </c>
       <c r="P2">
-        <v>1.049798862248529</v>
+        <v>1.049798862248525</v>
       </c>
       <c r="Q2">
-        <v>29.98859724152111</v>
+        <v>29.98859724152116</v>
       </c>
       <c r="R2">
-        <v>-90.01521016974866</v>
+        <v>-90.01521016974888</v>
       </c>
       <c r="S2">
-        <v>150.0038011686684</v>
+        <v>150.0038011686683</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -1051,55 +1051,55 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>0.0506694526399671</v>
+        <v>0.05066945263999146</v>
       </c>
       <c r="D3">
-        <v>0.0506694526399671</v>
+        <v>0.05066945263999144</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.01170160902291796</v>
+        <v>0.01170160902292359</v>
       </c>
       <c r="G3">
-        <v>0.01170160902291796</v>
+        <v>0.01170160902292358</v>
       </c>
       <c r="H3">
-        <v>2.048802864003135</v>
+        <v>2.048802864167397</v>
       </c>
       <c r="I3">
-        <v>1.383313298422268</v>
+        <v>1.383313298626652</v>
       </c>
       <c r="J3">
-        <v>0.5116671529773194</v>
+        <v>0.5116671529599571</v>
       </c>
       <c r="K3">
-        <v>0.3472468026119639</v>
+        <v>0.3472468025996517</v>
       </c>
       <c r="L3">
-        <v>0.5116671529773235</v>
+        <v>0.5116671529366223</v>
       </c>
       <c r="M3">
-        <v>0.3472468026119976</v>
+        <v>0.3472468026066617</v>
       </c>
       <c r="N3">
-        <v>1.002299347203498</v>
+        <v>1.002299347203896</v>
       </c>
       <c r="O3">
-        <v>0.8957178256710512</v>
+        <v>0.8957178256698493</v>
       </c>
       <c r="P3">
-        <v>1.024841978065004</v>
+        <v>1.024841978063851</v>
       </c>
       <c r="Q3">
-        <v>26.52931522749346</v>
+        <v>26.52931522749556</v>
       </c>
       <c r="R3">
-        <v>-88.39251432502026</v>
+        <v>-88.39251432507884</v>
       </c>
       <c r="S3">
-        <v>154.0981446418479</v>
+        <v>154.0981446419027</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -1143,22 +1143,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.002299347303008</v>
+        <v>1.002299347303482</v>
       </c>
       <c r="O4">
-        <v>0.8957178317817445</v>
+        <v>0.8957178317805766</v>
       </c>
       <c r="P4">
-        <v>1.024841980638074</v>
+        <v>1.02484198063662</v>
       </c>
       <c r="Q4">
-        <v>26.52931541744053</v>
+        <v>26.52931541743645</v>
       </c>
       <c r="R4">
-        <v>-88.39251415743716</v>
+        <v>-88.39251415752798</v>
       </c>
       <c r="S4">
-        <v>154.0981445241723</v>
+        <v>154.0981445242122</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -1202,22 +1202,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>1.002299347263204</v>
+        <v>1.00229934726351</v>
       </c>
       <c r="O5">
-        <v>0.8957178293374671</v>
+        <v>0.8957178293357486</v>
       </c>
       <c r="P5">
-        <v>1.024841979608846</v>
+        <v>1.02484197960712</v>
       </c>
       <c r="Q5">
-        <v>26.5293153414617</v>
+        <v>26.52931534146143</v>
       </c>
       <c r="R5">
-        <v>-88.3925142244704</v>
+        <v>-88.39251422455131</v>
       </c>
       <c r="S5">
-        <v>154.0981445712426</v>
+        <v>154.0981445713085</v>
       </c>
     </row>
   </sheetData>
@@ -1330,22 +1330,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.100044197268398</v>
+        <v>1.100044197268401</v>
       </c>
       <c r="O2">
         <v>1.099646973695688</v>
       </c>
       <c r="P2">
-        <v>1.099779330644697</v>
+        <v>1.099779330644694</v>
       </c>
       <c r="Q2">
-        <v>29.98805442002703</v>
+        <v>29.98805442002709</v>
       </c>
       <c r="R2">
-        <v>-90.01593423107204</v>
+        <v>-90.01593423107225</v>
       </c>
       <c r="S2">
-        <v>150.0039823002062</v>
+        <v>150.0039823002063</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -1356,55 +1356,55 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>0.0530815127807549</v>
+        <v>0.05308151278077346</v>
       </c>
       <c r="D3">
-        <v>0.0530815127807549</v>
+        <v>0.05308151278077346</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.01225865045985269</v>
+        <v>0.01225865045985697</v>
       </c>
       <c r="G3">
-        <v>0.01225865045985269</v>
+        <v>0.01225865045985697</v>
       </c>
       <c r="H3">
-        <v>2.04881092492271</v>
+        <v>2.048810925117779</v>
       </c>
       <c r="I3">
-        <v>1.383392955552335</v>
+        <v>1.383392955720942</v>
       </c>
       <c r="J3">
-        <v>0.5116751132846749</v>
+        <v>0.5116751132619101</v>
       </c>
       <c r="K3">
-        <v>0.3473264055688352</v>
+        <v>0.347326405539256</v>
       </c>
       <c r="L3">
-        <v>0.5116751132846632</v>
+        <v>0.5116751132525802</v>
       </c>
       <c r="M3">
-        <v>0.3473264055688411</v>
+        <v>0.3473264055744294</v>
       </c>
       <c r="N3">
-        <v>1.050030450405306</v>
+        <v>1.050030450406209</v>
       </c>
       <c r="O3">
-        <v>0.9383574270901905</v>
+        <v>0.9383574270889607</v>
       </c>
       <c r="P3">
-        <v>1.073635628315036</v>
+        <v>1.073635628314516</v>
       </c>
       <c r="Q3">
-        <v>26.52884014038561</v>
+        <v>26.52884014036632</v>
       </c>
       <c r="R3">
-        <v>-88.3932383862076</v>
+        <v>-88.39323838626153</v>
       </c>
       <c r="S3">
-        <v>154.0983225149558</v>
+        <v>154.0983225150189</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -1448,22 +1448,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.050030450509231</v>
+        <v>1.05003045051003</v>
       </c>
       <c r="O4">
-        <v>0.9383574334920346</v>
+        <v>0.9383574334906466</v>
       </c>
       <c r="P4">
-        <v>1.073635631011002</v>
+        <v>1.073635631010053</v>
       </c>
       <c r="Q4">
-        <v>26.52884033034576</v>
+        <v>26.52884033031895</v>
       </c>
       <c r="R4">
-        <v>-88.39323821857178</v>
+        <v>-88.39323821865327</v>
       </c>
       <c r="S4">
-        <v>154.0983223972833</v>
+        <v>154.098322397334</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -1507,22 +1507,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>1.050030450467661</v>
+        <v>1.050030450468467</v>
       </c>
       <c r="O5">
-        <v>0.938357430931297</v>
+        <v>0.9383574309295261</v>
       </c>
       <c r="P5">
-        <v>1.073635629932615</v>
+        <v>1.073635629931496</v>
       </c>
       <c r="Q5">
-        <v>26.5288402543617</v>
+        <v>26.52884025434003</v>
       </c>
       <c r="R5">
-        <v>-88.39323828562611</v>
+        <v>-88.39323828570238</v>
       </c>
       <c r="S5">
-        <v>154.0983224443523</v>
+        <v>154.0983224444265</v>
       </c>
     </row>
   </sheetData>
@@ -1635,22 +1635,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9504947120678211</v>
+        <v>0.9504947120678335</v>
       </c>
       <c r="O2">
-        <v>0.9492639078649421</v>
+        <v>0.9492639078649426</v>
       </c>
       <c r="P2">
-        <v>0.9491368456360405</v>
+        <v>0.9491368456360528</v>
       </c>
       <c r="Q2">
-        <v>29.95712896109838</v>
+        <v>29.95712896109875</v>
       </c>
       <c r="R2">
-        <v>-90.094618936343</v>
+        <v>-90.09461893634224</v>
       </c>
       <c r="S2">
-        <v>149.9956165875549</v>
+        <v>149.9956165875561</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -1661,55 +1661,55 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>0.1823567177694458</v>
+        <v>0.1823567177678155</v>
       </c>
       <c r="D3">
-        <v>0.1823567177694458</v>
+        <v>0.1823567177678155</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.04211348066463021</v>
+        <v>0.04211348066425372</v>
       </c>
       <c r="G3">
-        <v>0.04211348066463021</v>
+        <v>0.04211348066425372</v>
       </c>
       <c r="H3">
-        <v>3.933564400728234</v>
+        <v>3.933564400950151</v>
       </c>
       <c r="I3">
-        <v>1.380277273631228</v>
+        <v>1.380277273778748</v>
       </c>
       <c r="J3">
-        <v>0.9822689134097025</v>
+        <v>0.982268913438333</v>
       </c>
       <c r="K3">
-        <v>0.3474656432952729</v>
+        <v>0.3474656432863268</v>
       </c>
       <c r="L3">
-        <v>0.9822689134096926</v>
+        <v>0.9822689134386264</v>
       </c>
       <c r="M3">
-        <v>0.3474656432953018</v>
+        <v>0.3474656433264189</v>
       </c>
       <c r="N3">
-        <v>0.8227241232713736</v>
+        <v>0.8227241232789595</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>0.8227241232713804</v>
+        <v>0.8227241232815777</v>
       </c>
       <c r="Q3">
-        <v>8.244371258761251E-14</v>
+        <v>-7.916419987117949E-11</v>
       </c>
       <c r="R3">
         <v>0</v>
       </c>
       <c r="S3">
-        <v>179.9999999999926</v>
+        <v>179.9999999994634</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -1753,22 +1753,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8227241119861857</v>
+        <v>0.8227241119946079</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.8227241345565697</v>
+        <v>0.8227241345691217</v>
       </c>
       <c r="Q4">
-        <v>2.233477443745994E-06</v>
+        <v>2.233461245772163E-06</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>179.9999977665153</v>
+        <v>179.9999977657683</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -1812,22 +1812,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8227241165002603</v>
+        <v>0.8227241165080402</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0.8227241300424942</v>
+        <v>0.8227241300542772</v>
       </c>
       <c r="Q5">
-        <v>1.34008652936944E-06</v>
+        <v>1.340102594598777E-06</v>
       </c>
       <c r="R5">
         <v>0</v>
       </c>
       <c r="S5">
-        <v>179.9999986599062</v>
+        <v>179.9999986593054</v>
       </c>
     </row>
   </sheetData>
@@ -1940,22 +1940,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9004440553540198</v>
+        <v>0.9004440553540254</v>
       </c>
       <c r="O2">
-        <v>0.8993393732395855</v>
+        <v>0.8993393732395796</v>
       </c>
       <c r="P2">
-        <v>0.899225273740702</v>
+        <v>0.8992252737407059</v>
       </c>
       <c r="Q2">
-        <v>29.95938501571753</v>
+        <v>29.95938501571742</v>
       </c>
       <c r="R2">
-        <v>-90.08964264987587</v>
+        <v>-90.08964264987569</v>
       </c>
       <c r="S2">
-        <v>149.9958430352658</v>
+        <v>149.9958430352665</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -1966,55 +1966,55 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>0.1727660505215357</v>
+        <v>0.1727660505194399</v>
       </c>
       <c r="D3">
-        <v>0.1727660505215357</v>
+        <v>0.1727660505194399</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.03989861090471049</v>
+        <v>0.03989861090422646</v>
       </c>
       <c r="G3">
-        <v>0.03989861090471049</v>
+        <v>0.03989861090422646</v>
       </c>
       <c r="H3">
-        <v>3.93355421627931</v>
+        <v>3.933554215993011</v>
       </c>
       <c r="I3">
-        <v>1.380177713395197</v>
+        <v>1.380177713283042</v>
       </c>
       <c r="J3">
-        <v>0.9822589630274553</v>
+        <v>0.9822589630576509</v>
       </c>
       <c r="K3">
-        <v>0.3473661396185401</v>
+        <v>0.3473661396055267</v>
       </c>
       <c r="L3">
-        <v>0.9822589630274428</v>
+        <v>0.9822589630228384</v>
       </c>
       <c r="M3">
-        <v>0.3473661396185643</v>
+        <v>0.3473661396117605</v>
       </c>
       <c r="N3">
-        <v>0.7794228427583269</v>
+        <v>0.7794228427603641</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>0.7794228427583302</v>
+        <v>0.7794228427641845</v>
       </c>
       <c r="Q3">
-        <v>3.469473728784693E-14</v>
+        <v>-1.953886823464652E-10</v>
       </c>
       <c r="R3">
         <v>0</v>
       </c>
       <c r="S3">
-        <v>179.9999999999927</v>
+        <v>179.9999999997936</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -2058,22 +2058,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.7794228320670965</v>
+        <v>0.7794228320685856</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.7794228534495617</v>
+        <v>0.7794228534551485</v>
       </c>
       <c r="Q4">
-        <v>2.233477400849885E-06</v>
+        <v>2.233310358015714E-06</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>179.9999977665154</v>
+        <v>179.9999977662947</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -2117,22 +2117,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.7794228363435881</v>
+        <v>0.7794228363458089</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0.7794228491730694</v>
+        <v>0.7794228491804261</v>
       </c>
       <c r="Q5">
-        <v>1.340086485672968E-06</v>
+        <v>1.339986384842014E-06</v>
       </c>
       <c r="R5">
         <v>0</v>
       </c>
       <c r="S5">
-        <v>179.9999986599062</v>
+        <v>179.9999986596357</v>
       </c>
     </row>
   </sheetData>
@@ -2245,22 +2245,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9500519910672174</v>
+        <v>0.9500519910672208</v>
       </c>
       <c r="O2">
-        <v>0.9497163730518684</v>
+        <v>0.9497163730518657</v>
       </c>
       <c r="P2">
-        <v>0.9498061775520078</v>
+        <v>0.9498061775520101</v>
       </c>
       <c r="Q2">
-        <v>29.9883133724237</v>
+        <v>29.98831337242362</v>
       </c>
       <c r="R2">
-        <v>-90.01712266753385</v>
+        <v>-90.0171226675338</v>
       </c>
       <c r="S2">
-        <v>150.0031291278697</v>
+        <v>150.00312912787</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -2271,55 +2271,55 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>0.04223864396144971</v>
+        <v>0.0422386439613798</v>
       </c>
       <c r="D3">
-        <v>0.04223864396144972</v>
+        <v>0.04223864396137981</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.009754597129893924</v>
+        <v>0.009754597129877779</v>
       </c>
       <c r="G3">
-        <v>0.009754597129893926</v>
+        <v>0.009754597129877781</v>
       </c>
       <c r="H3">
-        <v>3.933564400728234</v>
+        <v>3.933564400950151</v>
       </c>
       <c r="I3">
-        <v>1.380277273631228</v>
+        <v>1.380277273778748</v>
       </c>
       <c r="J3">
-        <v>0.9822689134097025</v>
+        <v>0.982268913438333</v>
       </c>
       <c r="K3">
-        <v>0.3474656432952729</v>
+        <v>0.3474656432863268</v>
       </c>
       <c r="L3">
-        <v>0.9822689134096926</v>
+        <v>0.9822689134386264</v>
       </c>
       <c r="M3">
-        <v>0.3474656432953018</v>
+        <v>0.3474656433264189</v>
       </c>
       <c r="N3">
-        <v>0.8688824565885807</v>
+        <v>0.8688824565889276</v>
       </c>
       <c r="O3">
-        <v>0.7466807782052226</v>
+        <v>0.7466807782052592</v>
       </c>
       <c r="P3">
-        <v>0.9367813698662649</v>
+        <v>0.9367813698693714</v>
       </c>
       <c r="Q3">
-        <v>25.31117270792592</v>
+        <v>25.3111727077902</v>
       </c>
       <c r="R3">
-        <v>-84.27300812665352</v>
+        <v>-84.27300812653813</v>
       </c>
       <c r="S3">
-        <v>156.6375696710438</v>
+        <v>156.6375696710193</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -2363,22 +2363,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.868882460005816</v>
+        <v>0.8688824600066826</v>
       </c>
       <c r="O4">
-        <v>0.7466807938650381</v>
+        <v>0.7466807938660103</v>
       </c>
       <c r="P4">
-        <v>0.9367813729377028</v>
+        <v>0.9367813729419699</v>
       </c>
       <c r="Q4">
-        <v>25.31117317577862</v>
+        <v>25.31117317563863</v>
       </c>
       <c r="R4">
-        <v>-84.27300825578014</v>
+        <v>-84.27300825563718</v>
       </c>
       <c r="S4">
-        <v>156.6375692275357</v>
+        <v>156.6375692274932</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -2422,22 +2422,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8688824586389218</v>
+        <v>0.8688824586392562</v>
       </c>
       <c r="O5">
-        <v>0.7466807876011122</v>
+        <v>0.746680787601851</v>
       </c>
       <c r="P5">
-        <v>0.9367813717091278</v>
+        <v>0.9367813717127048</v>
       </c>
       <c r="Q5">
-        <v>25.31117298863755</v>
+        <v>25.31117298852318</v>
       </c>
       <c r="R5">
-        <v>-84.27300820412948</v>
+        <v>-84.27300820398068</v>
       </c>
       <c r="S5">
-        <v>156.6375694049389</v>
+        <v>156.6375694049024</v>
       </c>
     </row>
   </sheetData>
@@ -2550,22 +2550,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9000466517344052</v>
+        <v>0.9000466517344065</v>
       </c>
       <c r="O2">
-        <v>0.8997454277137985</v>
+        <v>0.8997454277137936</v>
       </c>
       <c r="P2">
-        <v>0.8998260263376501</v>
+        <v>0.8998260263376505</v>
       </c>
       <c r="Q2">
-        <v>29.98892829894006</v>
+        <v>29.98892829893984</v>
       </c>
       <c r="R2">
-        <v>-90.0162217294052</v>
+        <v>-90.01622172940525</v>
       </c>
       <c r="S2">
-        <v>150.0029642775241</v>
+        <v>150.0029642775244</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -2576,55 +2576,55 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>0.04001618573231812</v>
+        <v>0.04001618573223596</v>
       </c>
       <c r="D3">
-        <v>0.0400161857323181</v>
+        <v>0.04001618573223596</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.009241342379505101</v>
+        <v>0.009241342379486128</v>
       </c>
       <c r="G3">
-        <v>0.009241342379505099</v>
+        <v>0.009241342379486128</v>
       </c>
       <c r="H3">
-        <v>3.93355421627931</v>
+        <v>3.933554215993011</v>
       </c>
       <c r="I3">
-        <v>1.380177713395197</v>
+        <v>1.380177713283042</v>
       </c>
       <c r="J3">
-        <v>0.9822589630274553</v>
+        <v>0.9822589630576509</v>
       </c>
       <c r="K3">
-        <v>0.3473661396185401</v>
+        <v>0.3473661396055267</v>
       </c>
       <c r="L3">
-        <v>0.9822589630274428</v>
+        <v>0.9822589630228384</v>
       </c>
       <c r="M3">
-        <v>0.3473661396185643</v>
+        <v>0.3473661396117605</v>
       </c>
       <c r="N3">
-        <v>0.8231484127221256</v>
+        <v>0.823148412720813</v>
       </c>
       <c r="O3">
-        <v>0.7073928966725872</v>
+        <v>0.7073928966712167</v>
       </c>
       <c r="P3">
-        <v>0.8874846372706626</v>
+        <v>0.8874846372725484</v>
       </c>
       <c r="Q3">
-        <v>25.31166697432942</v>
+        <v>25.31166697421952</v>
       </c>
       <c r="R3">
-        <v>-84.27210718877164</v>
+        <v>-84.27210718856466</v>
       </c>
       <c r="S3">
-        <v>156.6374306578857</v>
+        <v>156.6374306579122</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -2668,22 +2668,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8231484159599609</v>
+        <v>0.8231484159587104</v>
       </c>
       <c r="O4">
-        <v>0.7073929115076905</v>
+        <v>0.7073929115064023</v>
       </c>
       <c r="P4">
-        <v>0.887484640179901</v>
+        <v>0.8874846401820266</v>
       </c>
       <c r="Q4">
-        <v>25.31166744215431</v>
+        <v>25.31166744203546</v>
       </c>
       <c r="R4">
-        <v>-84.27210731799734</v>
+        <v>-84.27210731778459</v>
       </c>
       <c r="S4">
-        <v>156.6374302143796</v>
+        <v>156.6374302144013</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -2727,22 +2727,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8231484146648267</v>
+        <v>0.8231484146635023</v>
       </c>
       <c r="O5">
-        <v>0.7073929055736495</v>
+        <v>0.7073929055729441</v>
       </c>
       <c r="P5">
-        <v>0.8874846390162058</v>
+        <v>0.8874846390185372</v>
       </c>
       <c r="Q5">
-        <v>25.31166725502436</v>
+        <v>25.31166725493582</v>
       </c>
       <c r="R5">
-        <v>-84.27210726630706</v>
+        <v>-84.27210726606666</v>
       </c>
       <c r="S5">
-        <v>156.637430391782</v>
+        <v>156.6374303917965</v>
       </c>
     </row>
   </sheetData>
@@ -2858,22 +2858,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.049226942770095</v>
+        <v>1.049226942770166</v>
       </c>
       <c r="O2">
-        <v>1.04999995231628</v>
+        <v>1.049999952316288</v>
       </c>
       <c r="P2">
-        <v>1.049860293027453</v>
+        <v>1.049860293027526</v>
       </c>
       <c r="Q2">
-        <v>29.98445362311656</v>
+        <v>29.98445362311615</v>
       </c>
       <c r="R2">
-        <v>-89.99999999999635</v>
+        <v>-89.99999999999464</v>
       </c>
       <c r="S2">
-        <v>149.9556948814871</v>
+        <v>149.9556948814907</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -2884,7 +2884,7 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>0.1961438699816457</v>
+        <v>0.1961438699686732</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -2893,7 +2893,7 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0.04529748712850438</v>
+        <v>0.04529748712550851</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -2902,43 +2902,43 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>2.048802864003164</v>
+        <v>2.048802864200902</v>
       </c>
       <c r="I3">
-        <v>1.38331329842227</v>
+        <v>1.383313298496587</v>
       </c>
       <c r="J3">
-        <v>0.5116671529774101</v>
+        <v>0.5116671529789214</v>
       </c>
       <c r="K3">
-        <v>0.3472468026119749</v>
+        <v>0.3472468026224648</v>
       </c>
       <c r="L3">
-        <v>0.5116671529773953</v>
+        <v>0.511667152990275</v>
       </c>
       <c r="M3">
-        <v>0.347246802612</v>
+        <v>0.3472468026513886</v>
       </c>
       <c r="N3">
-        <v>0.8015481718455055</v>
+        <v>0.8015481718556675</v>
       </c>
       <c r="O3">
-        <v>1.049999952316279</v>
+        <v>1.049999952327208</v>
       </c>
       <c r="P3">
-        <v>0.8021790979292637</v>
+        <v>0.8021790979654234</v>
       </c>
       <c r="Q3">
-        <v>40.87275499285191</v>
+        <v>40.87275499113137</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999589</v>
+        <v>-89.9999999997267</v>
       </c>
       <c r="S3">
-        <v>139.0751989924359</v>
+        <v>139.0751989925501</v>
       </c>
       <c r="T3">
-        <v>0.1961438699816457</v>
+        <v>0.1961438699686732</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -2982,22 +2982,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8015481846251941</v>
+        <v>0.8015481846347969</v>
       </c>
       <c r="O4">
-        <v>1.049999952316279</v>
+        <v>1.049999952322287</v>
       </c>
       <c r="P4">
-        <v>0.8021791012470415</v>
+        <v>0.8021791012856709</v>
       </c>
       <c r="Q4">
-        <v>40.87275488491994</v>
+        <v>40.87275488314362</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999588</v>
+        <v>-89.99999999936554</v>
       </c>
       <c r="S4">
-        <v>139.075199880503</v>
+        <v>139.0751998811449</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -3044,22 +3044,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8015481795133188</v>
+        <v>0.8015481795234034</v>
       </c>
       <c r="O5">
-        <v>1.049999952316279</v>
+        <v>1.049999952328854</v>
       </c>
       <c r="P5">
-        <v>0.8021790999199303</v>
+        <v>0.8021790999560043</v>
       </c>
       <c r="Q5">
-        <v>40.87275492809272</v>
+        <v>40.87275492625946</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999589</v>
+        <v>-89.99999999992271</v>
       </c>
       <c r="S5">
-        <v>139.0751995252762</v>
+        <v>139.0751995251119</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -3178,22 +3178,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.099151663051994</v>
+        <v>1.099151663052062</v>
       </c>
       <c r="O2">
-        <v>1.100000023841853</v>
+        <v>1.100000023841856</v>
       </c>
       <c r="P2">
-        <v>1.099846725405407</v>
+        <v>1.099846725405492</v>
       </c>
       <c r="Q2">
-        <v>29.98371562225426</v>
+        <v>29.98371562225271</v>
       </c>
       <c r="R2">
-        <v>-89.99999999999635</v>
+        <v>-89.99999999999493</v>
       </c>
       <c r="S2">
-        <v>149.9535871398336</v>
+        <v>149.9535871398364</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -3204,7 +3204,7 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>0.2054755534008091</v>
+        <v>0.2054755533864972</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0.04745254713423582</v>
+        <v>0.04745254713093064</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -3222,43 +3222,43 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>2.048810924922739</v>
+        <v>2.048810925143179</v>
       </c>
       <c r="I3">
-        <v>1.383392955552338</v>
+        <v>1.383392955596281</v>
       </c>
       <c r="J3">
-        <v>0.5116751132847441</v>
+        <v>0.511675113301345</v>
       </c>
       <c r="K3">
-        <v>0.3473264055688183</v>
+        <v>0.3473264055908857</v>
       </c>
       <c r="L3">
-        <v>0.5116751132847353</v>
+        <v>0.511675113291863</v>
       </c>
       <c r="M3">
-        <v>0.3473264055688434</v>
+        <v>0.3473264056029481</v>
       </c>
       <c r="N3">
-        <v>0.8396969228492067</v>
+        <v>0.8396969228516016</v>
       </c>
       <c r="O3">
-        <v>1.100000023841853</v>
+        <v>1.100000023850102</v>
       </c>
       <c r="P3">
-        <v>0.8403785429622926</v>
+        <v>0.8403785429975333</v>
       </c>
       <c r="Q3">
-        <v>40.87252921037393</v>
+        <v>40.87252920861007</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999589</v>
+        <v>-89.99999999972637</v>
       </c>
       <c r="S3">
-        <v>139.0737992409941</v>
+        <v>139.0737992407105</v>
       </c>
       <c r="T3">
-        <v>0.2054755534008091</v>
+        <v>0.2054755533864972</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -3302,22 +3302,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8396969362380932</v>
+        <v>0.8396969362384613</v>
       </c>
       <c r="O4">
-        <v>1.100000023841853</v>
+        <v>1.100000023848318</v>
       </c>
       <c r="P4">
-        <v>0.8403785464372405</v>
+        <v>0.8403785464739125</v>
       </c>
       <c r="Q4">
-        <v>40.87252910248374</v>
+        <v>40.87252910067588</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999589</v>
+        <v>-89.9999999995712</v>
       </c>
       <c r="S4">
-        <v>139.0738001291151</v>
+        <v>139.0738001289134</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -3364,22 +3364,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8396969308825385</v>
+        <v>0.8396969308848526</v>
       </c>
       <c r="O5">
-        <v>1.100000023841853</v>
+        <v>1.100000023851826</v>
       </c>
       <c r="P5">
-        <v>0.8403785450472612</v>
+        <v>0.8403785450824125</v>
       </c>
       <c r="Q5">
-        <v>40.87252914563982</v>
+        <v>40.87252914376322</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999589</v>
+        <v>-89.99999999992238</v>
       </c>
       <c r="S5">
-        <v>139.0737997738667</v>
+        <v>139.0737997733047</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -3498,22 +3498,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.049879294950495</v>
+        <v>1.0498792949505</v>
       </c>
       <c r="O2">
-        <v>1.049999952316284</v>
+        <v>1.049999952316286</v>
       </c>
       <c r="P2">
-        <v>1.049959770497422</v>
+        <v>1.049959770497431</v>
       </c>
       <c r="Q2">
-        <v>29.99873081648546</v>
+        <v>29.99873081648531</v>
       </c>
       <c r="R2">
-        <v>-89.99999999999635</v>
+        <v>-89.99999999999609</v>
       </c>
       <c r="S2">
-        <v>149.993663349747</v>
+        <v>149.9936633497472</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -3524,7 +3524,7 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>0.02925678275263625</v>
+        <v>0.02925678275235446</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -3533,7 +3533,7 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0.006756564659823432</v>
+        <v>0.006756564659758357</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -3542,43 +3542,43 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>2.048802864003164</v>
+        <v>2.048802864200902</v>
       </c>
       <c r="I3">
-        <v>1.38331329842227</v>
+        <v>1.383313298496587</v>
       </c>
       <c r="J3">
-        <v>0.5116671529774101</v>
+        <v>0.5116671529789214</v>
       </c>
       <c r="K3">
-        <v>0.3472468026119749</v>
+        <v>0.3472468026224648</v>
       </c>
       <c r="L3">
-        <v>0.5116671529773953</v>
+        <v>0.511667152990275</v>
       </c>
       <c r="M3">
-        <v>0.347246802612</v>
+        <v>0.3472468026513886</v>
       </c>
       <c r="N3">
-        <v>1.015361077962755</v>
+        <v>1.015361077963079</v>
       </c>
       <c r="O3">
-        <v>1.049999952316284</v>
+        <v>1.049999952318143</v>
       </c>
       <c r="P3">
-        <v>1.007841946611173</v>
+        <v>1.007841946614584</v>
       </c>
       <c r="Q3">
-        <v>31.61386361990858</v>
+        <v>31.61386361979187</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999629</v>
+        <v>-89.99999999996629</v>
       </c>
       <c r="S3">
-        <v>149.0875829960723</v>
+        <v>149.0875829959597</v>
       </c>
       <c r="T3">
-        <v>0.02925678275263625</v>
+        <v>0.02925678275235446</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -3622,22 +3622,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.015361079868778</v>
+        <v>1.015361079869085</v>
       </c>
       <c r="O4">
-        <v>1.049999952316284</v>
+        <v>1.049999952317413</v>
       </c>
       <c r="P4">
-        <v>1.007841947691761</v>
+        <v>1.007841947695765</v>
       </c>
       <c r="Q4">
-        <v>31.61386360710813</v>
+        <v>31.61386360698439</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999629</v>
+        <v>-89.99999999991128</v>
       </c>
       <c r="S4">
-        <v>149.08758308626</v>
+        <v>149.0875830862083</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -3684,22 +3684,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>1.015361079106369</v>
+        <v>1.015361079106823</v>
       </c>
       <c r="O5">
-        <v>1.049999952316284</v>
+        <v>1.049999952318433</v>
       </c>
       <c r="P5">
-        <v>1.007841947259526</v>
+        <v>1.007841947262916</v>
       </c>
       <c r="Q5">
-        <v>31.61386361222831</v>
+        <v>31.61386361209446</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999629</v>
+        <v>-89.99999999999808</v>
       </c>
       <c r="S5">
-        <v>149.0875830501849</v>
+        <v>149.0875830500398</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -3943,22 +3943,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.099867602508712</v>
+        <v>1.099867602508715</v>
       </c>
       <c r="O2">
-        <v>1.100000023841857</v>
+        <v>1.100000023841858</v>
       </c>
       <c r="P2">
-        <v>1.099955923916905</v>
+        <v>1.099955923916915</v>
       </c>
       <c r="Q2">
-        <v>29.99867042519999</v>
+        <v>29.99867042519972</v>
       </c>
       <c r="R2">
-        <v>-89.99999999999635</v>
+        <v>-89.99999999999609</v>
       </c>
       <c r="S2">
-        <v>149.9933616553705</v>
+        <v>149.9933616553706</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -3969,7 +3969,7 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>0.03064974122581553</v>
+        <v>0.03064974122551201</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -3978,7 +3978,7 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0.007078254644401</v>
+        <v>0.007078254644330904</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -3987,43 +3987,43 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>2.048810924922739</v>
+        <v>2.048810925143179</v>
       </c>
       <c r="I3">
-        <v>1.383392955552338</v>
+        <v>1.383392955596281</v>
       </c>
       <c r="J3">
-        <v>0.5116751132847441</v>
+        <v>0.511675113301345</v>
       </c>
       <c r="K3">
-        <v>0.3473264055688183</v>
+        <v>0.3473264055908857</v>
       </c>
       <c r="L3">
-        <v>0.5116751132847353</v>
+        <v>0.511675113291863</v>
       </c>
       <c r="M3">
-        <v>0.3473264055688434</v>
+        <v>0.3473264056029481</v>
       </c>
       <c r="N3">
-        <v>1.063706084863743</v>
+        <v>1.06370608486281</v>
       </c>
       <c r="O3">
-        <v>1.100000023841857</v>
+        <v>1.100000023843486</v>
       </c>
       <c r="P3">
-        <v>1.055832789376986</v>
+        <v>1.055832789379671</v>
       </c>
       <c r="Q3">
-        <v>31.61381031032723</v>
+        <v>31.6138103102302</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999629</v>
+        <v>-89.99999999995501</v>
       </c>
       <c r="S3">
-        <v>149.0872889872169</v>
+        <v>149.0872889870731</v>
       </c>
       <c r="T3">
-        <v>0.03064974122581553</v>
+        <v>0.03064974122551201</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -4067,22 +4067,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.063706086860703</v>
+        <v>1.06370608685952</v>
       </c>
       <c r="O4">
-        <v>1.100000023841857</v>
+        <v>1.100000023843223</v>
       </c>
       <c r="P4">
-        <v>1.055832790508953</v>
+        <v>1.055832790511858</v>
       </c>
       <c r="Q4">
-        <v>31.61381029753585</v>
+        <v>31.61381029743312</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999629</v>
+        <v>-89.9999999999321</v>
       </c>
       <c r="S4">
-        <v>149.0872890774176</v>
+        <v>149.0872890772836</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -4129,22 +4129,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>1.063706086061919</v>
+        <v>1.063706086061123</v>
       </c>
       <c r="O5">
-        <v>1.100000023841857</v>
+        <v>1.10000002384379</v>
       </c>
       <c r="P5">
-        <v>1.055832790056166</v>
+        <v>1.055832790058829</v>
       </c>
       <c r="Q5">
-        <v>31.6138103026524</v>
+        <v>31.6138103025382</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999629</v>
+        <v>-89.99999999998681</v>
       </c>
       <c r="S5">
-        <v>149.0872890413373</v>
+        <v>149.0872890411609</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -4263,22 +4263,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9495899703454644</v>
+        <v>0.9495899703454814</v>
       </c>
       <c r="O2">
-        <v>0.9499999880790715</v>
+        <v>0.9499999880790841</v>
       </c>
       <c r="P2">
-        <v>0.9500428745733643</v>
+        <v>0.9500428745733545</v>
       </c>
       <c r="Q2">
-        <v>29.98273632820458</v>
+        <v>29.98273632820589</v>
       </c>
       <c r="R2">
-        <v>-89.99999999999635</v>
+        <v>-89.99999999999676</v>
       </c>
       <c r="S2">
-        <v>149.9699552917309</v>
+        <v>149.9699552917316</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -4289,7 +4289,7 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>0.1052661193026717</v>
+        <v>0.1052661192970085</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -4298,7 +4298,7 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0.02431016928862766</v>
+        <v>0.0243101692873198</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -4307,43 +4307,43 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>3.933564400728284</v>
+        <v>3.933564400979036</v>
       </c>
       <c r="I3">
-        <v>1.38027727363123</v>
+        <v>1.380277273848993</v>
       </c>
       <c r="J3">
-        <v>0.982268913409819</v>
+        <v>0.9822689134123498</v>
       </c>
       <c r="K3">
-        <v>0.347465643295257</v>
+        <v>0.3474656433491256</v>
       </c>
       <c r="L3">
-        <v>0.9822689134098265</v>
+        <v>0.9822689134193464</v>
       </c>
       <c r="M3">
-        <v>0.347465643295304</v>
+        <v>0.3474656432902385</v>
       </c>
       <c r="N3">
-        <v>0.7253070805808111</v>
+        <v>0.7253070805946787</v>
       </c>
       <c r="O3">
-        <v>0.9499999880790715</v>
+        <v>0.9499999880786806</v>
       </c>
       <c r="P3">
-        <v>0.725911863146719</v>
+        <v>0.725911863148752</v>
       </c>
       <c r="Q3">
-        <v>40.86342210870047</v>
+        <v>40.86342210820997</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999589</v>
+        <v>-90.00000000046191</v>
       </c>
       <c r="S3">
-        <v>139.0814304927861</v>
+        <v>139.0814304934232</v>
       </c>
       <c r="T3">
-        <v>0.1052661193026717</v>
+        <v>0.1052661192970085</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -4387,22 +4387,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.7253070988559559</v>
+        <v>0.7253070988706876</v>
       </c>
       <c r="O4">
-        <v>0.9499999880790715</v>
+        <v>0.9499999880793276</v>
       </c>
       <c r="P4">
-        <v>0.7259118728404218</v>
+        <v>0.725911872841378</v>
       </c>
       <c r="Q4">
-        <v>40.86342154349578</v>
+        <v>40.86342154295953</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999589</v>
+        <v>-90.00000000063727</v>
       </c>
       <c r="S4">
-        <v>139.081431839697</v>
+        <v>139.0814318402062</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -4449,22 +4449,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.7253070915458983</v>
+        <v>0.7253070915609069</v>
       </c>
       <c r="O5">
-        <v>0.9499999880790715</v>
+        <v>0.9499999880813121</v>
       </c>
       <c r="P5">
-        <v>0.7259118689629408</v>
+        <v>0.7259118689648881</v>
       </c>
       <c r="Q5">
-        <v>40.86342176957764</v>
+        <v>40.8634217688844</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999589</v>
+        <v>-90.00000000082207</v>
       </c>
       <c r="S5">
-        <v>139.0814313009327</v>
+        <v>139.0814313011643</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -4583,22 +4583,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.8996319840317653</v>
+        <v>0.8996319840317428</v>
       </c>
       <c r="O2">
-        <v>0.8999999761581394</v>
+        <v>0.8999999761581369</v>
       </c>
       <c r="P2">
-        <v>0.9000384811266839</v>
+        <v>0.9000384811266734</v>
       </c>
       <c r="Q2">
-        <v>29.98364396239909</v>
+        <v>29.98364396239858</v>
       </c>
       <c r="R2">
-        <v>-89.99999999999635</v>
+        <v>-89.9999999999967</v>
       </c>
       <c r="S2">
-        <v>149.9715360509975</v>
+        <v>149.971536050996</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -4609,7 +4609,7 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>0.0997278289626669</v>
+        <v>0.09972782896751022</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -4618,7 +4618,7 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0.02303115590210804</v>
+        <v>0.02303115590322656</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -4627,43 +4627,43 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>3.933554216279361</v>
+        <v>3.933554215957431</v>
       </c>
       <c r="I3">
-        <v>1.380177713395198</v>
+        <v>1.380177713378632</v>
       </c>
       <c r="J3">
-        <v>0.9822589630275964</v>
+        <v>0.9822589630197631</v>
       </c>
       <c r="K3">
-        <v>0.3473661396185194</v>
+        <v>0.3473661396591991</v>
       </c>
       <c r="L3">
-        <v>0.9822589630275768</v>
+        <v>0.9822589630179832</v>
       </c>
       <c r="M3">
-        <v>0.3473661396185667</v>
+        <v>0.3473661396440931</v>
       </c>
       <c r="N3">
-        <v>0.687144402043</v>
+        <v>0.687144402035396</v>
       </c>
       <c r="O3">
-        <v>0.8999999761581394</v>
+        <v>0.8999999761546016</v>
       </c>
       <c r="P3">
-        <v>0.6877025778260556</v>
+        <v>0.6877025778113849</v>
       </c>
       <c r="Q3">
-        <v>40.86384470191874</v>
+        <v>40.86384470287376</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999589</v>
+        <v>-89.99999999999007</v>
       </c>
       <c r="S3">
-        <v>139.0824298864973</v>
+        <v>139.0824298862344</v>
       </c>
       <c r="T3">
-        <v>0.09972782896266688</v>
+        <v>0.0997278289675102</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -4707,22 +4707,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.6871444193555964</v>
+        <v>0.6871444193498755</v>
       </c>
       <c r="O4">
-        <v>0.8999999761581394</v>
+        <v>0.8999999761544045</v>
       </c>
       <c r="P4">
-        <v>0.6877025870103592</v>
+        <v>0.6877025869993748</v>
       </c>
       <c r="Q4">
-        <v>40.86384413666168</v>
+        <v>40.86384413760954</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999589</v>
+        <v>-89.99999999969845</v>
       </c>
       <c r="S4">
-        <v>139.0824312333408</v>
+        <v>139.0824312334946</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -4769,22 +4769,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.687144412430558</v>
+        <v>0.6871444124240347</v>
       </c>
       <c r="O5">
-        <v>0.8999999761581394</v>
+        <v>0.8999999761570947</v>
       </c>
       <c r="P5">
-        <v>0.6877025833366379</v>
+        <v>0.6877025833218861</v>
       </c>
       <c r="Q5">
-        <v>40.8638443627645</v>
+        <v>40.86384436351678</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999589</v>
+        <v>-90.00000000035021</v>
       </c>
       <c r="S5">
-        <v>139.0824306946034</v>
+        <v>139.082430693935</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -4903,22 +4903,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9498881090148399</v>
+        <v>0.9498881090148401</v>
       </c>
       <c r="O2">
-        <v>0.949999988079071</v>
+        <v>0.9499999880790728</v>
       </c>
       <c r="P2">
-        <v>0.9499700858544576</v>
+        <v>0.9499700858544572</v>
       </c>
       <c r="Q2">
         <v>29.99818695071847</v>
       </c>
       <c r="R2">
-        <v>-89.99999999999635</v>
+        <v>-89.99999999999645</v>
       </c>
       <c r="S2">
-        <v>149.9932497715758</v>
+        <v>149.9932497715756</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -4929,7 +4929,7 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>0.02438883360420217</v>
+        <v>0.02438883360386583</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -4938,7 +4938,7 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0.005632359942571549</v>
+        <v>0.005632359942493873</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -4947,43 +4947,43 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>3.933564400728284</v>
+        <v>3.933564400979036</v>
       </c>
       <c r="I3">
-        <v>1.38027727363123</v>
+        <v>1.380277273848993</v>
       </c>
       <c r="J3">
-        <v>0.982268913409819</v>
+        <v>0.9822689134123498</v>
       </c>
       <c r="K3">
-        <v>0.347465643295257</v>
+        <v>0.3474656433491256</v>
       </c>
       <c r="L3">
-        <v>0.9822689134098265</v>
+        <v>0.9822689134193464</v>
       </c>
       <c r="M3">
-        <v>0.347465643295304</v>
+        <v>0.3474656432902385</v>
       </c>
       <c r="N3">
-        <v>0.9102637354936918</v>
+        <v>0.9102637354937271</v>
       </c>
       <c r="O3">
-        <v>0.949999988079071</v>
+        <v>0.9499999880786464</v>
       </c>
       <c r="P3">
-        <v>0.8875538273748504</v>
+        <v>0.8875538273736355</v>
       </c>
       <c r="Q3">
-        <v>33.05430924257372</v>
+        <v>33.05430924256711</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999625</v>
+        <v>-90.00000000007398</v>
       </c>
       <c r="S3">
-        <v>149.2716838231431</v>
+        <v>149.2716838231232</v>
       </c>
       <c r="T3">
-        <v>0.02438883360420217</v>
+        <v>0.02438883360386583</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -5027,22 +5027,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.910263739288095</v>
+        <v>0.9102637392883157</v>
       </c>
       <c r="O4">
-        <v>0.949999988079071</v>
+        <v>0.9499999880789385</v>
       </c>
       <c r="P4">
-        <v>0.8875538312990119</v>
+        <v>0.8875538312976694</v>
       </c>
       <c r="Q4">
-        <v>33.05430908485783</v>
+        <v>33.05430908484679</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999625</v>
+        <v>-90.00000000010357</v>
       </c>
       <c r="S4">
-        <v>149.2716839714325</v>
+        <v>149.2716839713889</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -5089,22 +5089,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9102637377703338</v>
+        <v>0.9102637377707754</v>
       </c>
       <c r="O5">
-        <v>0.949999988079071</v>
+        <v>0.9499999880790508</v>
       </c>
       <c r="P5">
-        <v>0.8875538297293475</v>
+        <v>0.8875538297275117</v>
       </c>
       <c r="Q5">
-        <v>33.05430914794419</v>
+        <v>33.05430914792462</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999625</v>
+        <v>-90.0000000001576</v>
       </c>
       <c r="S5">
-        <v>149.2716839121167</v>
+        <v>149.2716839120463</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -5223,22 +5223,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.8998995633246877</v>
+        <v>0.8998995633246843</v>
       </c>
       <c r="O2">
-        <v>0.8999999761581415</v>
+        <v>0.8999999761581398</v>
       </c>
       <c r="P2">
-        <v>0.8999731389721763</v>
+        <v>0.8999731389721715</v>
       </c>
       <c r="Q2">
-        <v>29.99828232124134</v>
+        <v>29.99828232124138</v>
       </c>
       <c r="R2">
-        <v>-89.99999999999635</v>
+        <v>-89.99999999999648</v>
       </c>
       <c r="S2">
-        <v>149.9936049936319</v>
+        <v>149.9936049936318</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -5249,7 +5249,7 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>0.02310539214590443</v>
+        <v>0.02310539214610254</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -5258,7 +5258,7 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0.005335961829579941</v>
+        <v>0.005335961829625692</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -5267,43 +5267,43 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>3.933554216279361</v>
+        <v>3.933554215957431</v>
       </c>
       <c r="I3">
-        <v>1.380177713395198</v>
+        <v>1.380177713378632</v>
       </c>
       <c r="J3">
-        <v>0.9822589630275964</v>
+        <v>0.9822589630197631</v>
       </c>
       <c r="K3">
-        <v>0.3473661396185194</v>
+        <v>0.3473661396591991</v>
       </c>
       <c r="L3">
-        <v>0.9822589630275768</v>
+        <v>0.9822589630179832</v>
       </c>
       <c r="M3">
-        <v>0.3473661396185667</v>
+        <v>0.3473661396440931</v>
       </c>
       <c r="N3">
-        <v>0.8623600932803913</v>
+        <v>0.8623600932800334</v>
       </c>
       <c r="O3">
-        <v>0.8999999761581415</v>
+        <v>0.8999999761566391</v>
       </c>
       <c r="P3">
-        <v>0.8408415018635509</v>
+        <v>0.8408415018613912</v>
       </c>
       <c r="Q3">
-        <v>33.05439499025354</v>
+        <v>33.05439499038046</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999626</v>
+        <v>-89.99999999996072</v>
       </c>
       <c r="S3">
-        <v>149.2720275626354</v>
+        <v>149.2720275627785</v>
       </c>
       <c r="T3">
-        <v>0.02310539214590443</v>
+        <v>0.02310539214610254</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -5347,22 +5347,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8623600968747794</v>
+        <v>0.8623600968749066</v>
       </c>
       <c r="O4">
-        <v>0.8999999761581415</v>
+        <v>0.8999999761569629</v>
       </c>
       <c r="P4">
-        <v>0.84084150558124</v>
+        <v>0.8408415055801652</v>
       </c>
       <c r="Q4">
-        <v>33.05439483252454</v>
+        <v>33.05439483266308</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999625</v>
+        <v>-89.99999999989684</v>
       </c>
       <c r="S4">
-        <v>149.2720277108982</v>
+        <v>149.2720277110921</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -5409,22 +5409,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8623600954370242</v>
+        <v>0.8623600954370512</v>
       </c>
       <c r="O5">
-        <v>0.8999999761581415</v>
+        <v>0.8999999761570222</v>
       </c>
       <c r="P5">
-        <v>0.8408415040941642</v>
+        <v>0.8408415040914162</v>
       </c>
       <c r="Q5">
-        <v>33.05439489561613</v>
+        <v>33.0543948957301</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999625</v>
+        <v>-90.00000000004432</v>
       </c>
       <c r="S5">
-        <v>149.2720276515931</v>
+        <v>149.2720276516856</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -5543,22 +5543,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.050234052937961</v>
+        <v>1.050234052937969</v>
       </c>
       <c r="O2">
-        <v>1.048173411570604</v>
+        <v>1.048173411570587</v>
       </c>
       <c r="P2">
-        <v>1.048548232600658</v>
+        <v>1.048548232600595</v>
       </c>
       <c r="Q2">
-        <v>29.92175272018186</v>
+        <v>29.92175272018378</v>
       </c>
       <c r="R2">
-        <v>-90.11967249081198</v>
+        <v>-90.11967249081376</v>
       </c>
       <c r="S2">
-        <v>149.9985745740005</v>
+        <v>149.9985745740018</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -5572,58 +5572,58 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>0.3459755857711127</v>
+        <v>0.3459755857683853</v>
       </c>
       <c r="D3">
-        <v>0.3457034707010911</v>
+        <v>0.3457034707011522</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.07989964022179356</v>
+        <v>0.07989964022116368</v>
       </c>
       <c r="G3">
-        <v>0.07983679793728612</v>
+        <v>0.07983679793730024</v>
       </c>
       <c r="H3">
-        <v>2.048802864003135</v>
+        <v>2.048802864167397</v>
       </c>
       <c r="I3">
-        <v>1.383313298422268</v>
+        <v>1.383313298626652</v>
       </c>
       <c r="J3">
-        <v>0.5116671529773194</v>
+        <v>0.5116671529599571</v>
       </c>
       <c r="K3">
-        <v>0.3472468026119639</v>
+        <v>0.3472468025996517</v>
       </c>
       <c r="L3">
-        <v>0.5116671529773235</v>
+        <v>0.5116671529366223</v>
       </c>
       <c r="M3">
-        <v>0.3472468026119976</v>
+        <v>0.3472468026066617</v>
       </c>
       <c r="N3">
-        <v>0.8082392293687279</v>
+        <v>0.8082392293762495</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>0.8082392293687033</v>
+        <v>0.8082392293733981</v>
       </c>
       <c r="Q3">
-        <v>-0.01518448049999265</v>
+        <v>-0.01518447971802059</v>
       </c>
       <c r="R3">
         <v>0</v>
       </c>
       <c r="S3">
-        <v>179.9848155194906</v>
+        <v>179.9848155212159</v>
       </c>
       <c r="T3">
-        <v>0.1307791446093346</v>
+        <v>0.1307791445982361</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -5667,22 +5667,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8082392204398072</v>
+        <v>0.8082392204479948</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.8082392453957743</v>
+        <v>0.808239245394656</v>
       </c>
       <c r="Q4">
-        <v>-0.01518300111962987</v>
+        <v>-0.01518300026509494</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>179.9848143818178</v>
+        <v>179.9848143834887</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -5729,22 +5729,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8082392240113753</v>
+        <v>0.8082392240176344</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0.8082392389849463</v>
+        <v>0.8082392389880783</v>
       </c>
       <c r="Q5">
-        <v>-0.01518359287177051</v>
+        <v>-0.01518359206209005</v>
       </c>
       <c r="R5">
         <v>0</v>
       </c>
       <c r="S5">
-        <v>179.9848148368869</v>
+        <v>179.9848148389578</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -5863,22 +5863,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.100256815443185</v>
+        <v>1.100256815443219</v>
       </c>
       <c r="O2">
-        <v>1.09799543167444</v>
+        <v>1.097995431674414</v>
       </c>
       <c r="P2">
-        <v>1.098406899252609</v>
+        <v>1.098406899252564</v>
       </c>
       <c r="Q2">
-        <v>29.91803171923368</v>
+        <v>29.91803171923491</v>
       </c>
       <c r="R2">
-        <v>-90.12536079167887</v>
+        <v>-90.12536079168059</v>
       </c>
       <c r="S2">
-        <v>149.9985139394172</v>
+        <v>149.9985139394196</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -5892,58 +5892,58 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>0.3624257463710422</v>
+        <v>0.3624257463715317</v>
       </c>
       <c r="D3">
-        <v>0.3621317875589192</v>
+        <v>0.3621317875585172</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.08369864213863584</v>
+        <v>0.08369864213874888</v>
       </c>
       <c r="G3">
-        <v>0.08363075525790029</v>
+        <v>0.08363075525780746</v>
       </c>
       <c r="H3">
-        <v>2.04881092492271</v>
+        <v>2.048810925117779</v>
       </c>
       <c r="I3">
-        <v>1.383392955552335</v>
+        <v>1.383392955720942</v>
       </c>
       <c r="J3">
-        <v>0.5116751132846749</v>
+        <v>0.5116751132619101</v>
       </c>
       <c r="K3">
-        <v>0.3473264055688352</v>
+        <v>0.347326405539256</v>
       </c>
       <c r="L3">
-        <v>0.5116751132846632</v>
+        <v>0.5116751132525802</v>
       </c>
       <c r="M3">
-        <v>0.3473264055688411</v>
+        <v>0.3473264055744294</v>
       </c>
       <c r="N3">
-        <v>0.8467210279325773</v>
+        <v>0.8467210279465175</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>0.8467210279325691</v>
+        <v>0.846721027946123</v>
       </c>
       <c r="Q3">
-        <v>-0.0156592257915673</v>
+        <v>-0.01565922554282706</v>
       </c>
       <c r="R3">
         <v>0</v>
       </c>
       <c r="S3">
-        <v>179.9843407742001</v>
+        <v>179.9843407754452</v>
       </c>
       <c r="T3">
-        <v>0.1370029464599702</v>
+        <v>0.1370029464496659</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -5987,22 +5987,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.846721018578327</v>
+        <v>0.8467210185931258</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.8467210447230132</v>
+        <v>0.8467210447327723</v>
       </c>
       <c r="Q4">
-        <v>-0.01565774638016302</v>
+        <v>-0.01565774605150279</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>179.9843396365551</v>
+        <v>179.9843396379124</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -6049,22 +6049,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8467210223200269</v>
+        <v>0.8467210223326442</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0.8467210380068357</v>
+        <v>0.8467210380187524</v>
       </c>
       <c r="Q5">
-        <v>-0.01565833814471741</v>
+        <v>-0.01565833786826649</v>
       </c>
       <c r="R5">
         <v>0</v>
       </c>
       <c r="S5">
-        <v>179.9843400916131</v>
+        <v>179.9843400932037</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -6183,19 +6183,19 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.049964148037377</v>
+        <v>1.049964148037376</v>
       </c>
       <c r="O2">
-        <v>1.049824400685046</v>
+        <v>1.049824400685044</v>
       </c>
       <c r="P2">
-        <v>1.049873815726591</v>
+        <v>1.049873815726581</v>
       </c>
       <c r="Q2">
-        <v>29.99320494129953</v>
+        <v>29.99320494129977</v>
       </c>
       <c r="R2">
-        <v>-90.00808470234183</v>
+        <v>-90.00808470234212</v>
       </c>
       <c r="S2">
         <v>149.9991649635709</v>
@@ -6212,58 +6212,58 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>0.03084976925761263</v>
+        <v>0.03084976925745735</v>
       </c>
       <c r="D3">
-        <v>0.03025270750134595</v>
+        <v>0.03025270750124391</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.007124449140290762</v>
+        <v>0.007124449140254902</v>
       </c>
       <c r="G3">
-        <v>0.006986563631954748</v>
+        <v>0.006986563631931182</v>
       </c>
       <c r="H3">
-        <v>2.048802864003135</v>
+        <v>2.048802864167397</v>
       </c>
       <c r="I3">
-        <v>1.383313298422268</v>
+        <v>1.383313298626652</v>
       </c>
       <c r="J3">
-        <v>0.5116671529773194</v>
+        <v>0.5116671529599571</v>
       </c>
       <c r="K3">
-        <v>0.3472468026119639</v>
+        <v>0.3472468025996517</v>
       </c>
       <c r="L3">
-        <v>0.5116671529773235</v>
+        <v>0.5116671529366223</v>
       </c>
       <c r="M3">
-        <v>0.3472468026119976</v>
+        <v>0.3472468026066617</v>
       </c>
       <c r="N3">
-        <v>1.006558191833886</v>
+        <v>1.006558191834797</v>
       </c>
       <c r="O3">
-        <v>0.9668366588206877</v>
+        <v>0.9668366588187991</v>
       </c>
       <c r="P3">
-        <v>1.016417179316686</v>
+        <v>1.016417179314449</v>
       </c>
       <c r="Q3">
-        <v>28.90317285753057</v>
+        <v>28.90317285760926</v>
       </c>
       <c r="R3">
-        <v>-89.13252169220242</v>
+        <v>-89.13252169224673</v>
       </c>
       <c r="S3">
-        <v>151.805341253846</v>
+        <v>151.805341254004</v>
       </c>
       <c r="T3">
-        <v>0.02725059742806405</v>
+        <v>0.02725059742757435</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -6307,22 +6307,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.006558192877255</v>
+        <v>1.006558192878358</v>
       </c>
       <c r="O4">
-        <v>0.9668366621186248</v>
+        <v>0.9668366621171682</v>
       </c>
       <c r="P4">
-        <v>1.016417181265221</v>
+        <v>1.016417181262188</v>
       </c>
       <c r="Q4">
-        <v>28.90317295625301</v>
+        <v>28.9031729563469</v>
       </c>
       <c r="R4">
-        <v>-89.13252160841085</v>
+        <v>-89.13252160851521</v>
       </c>
       <c r="S4">
-        <v>151.8053412325514</v>
+        <v>151.8053412326777</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -6369,22 +6369,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>1.006558192459908</v>
+        <v>1.006558192460617</v>
       </c>
       <c r="O5">
-        <v>0.96683666079945</v>
+        <v>0.9668366607970246</v>
       </c>
       <c r="P5">
-        <v>1.016417180485807</v>
+        <v>1.016417180483359</v>
       </c>
       <c r="Q5">
-        <v>28.90317291676403</v>
+        <v>28.90317291685507</v>
       </c>
       <c r="R5">
-        <v>-89.13252164192748</v>
+        <v>-89.13252164194866</v>
       </c>
       <c r="S5">
-        <v>151.8053412410692</v>
+        <v>151.8053412412615</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -6503,22 +6503,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.099960728154766</v>
+        <v>1.099960728154768</v>
       </c>
       <c r="O2">
-        <v>1.099807355906276</v>
+        <v>1.099807355906275</v>
       </c>
       <c r="P2">
-        <v>1.09986158922622</v>
+        <v>1.099861589226214</v>
       </c>
       <c r="Q2">
-        <v>29.9928814227177</v>
+        <v>29.99288142271792</v>
       </c>
       <c r="R2">
-        <v>-90.00846962073501</v>
+        <v>-90.00846962073528</v>
       </c>
       <c r="S2">
-        <v>149.9991252457516</v>
+        <v>149.9991252457517</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -6532,58 +6532,58 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>0.03231856841214049</v>
+        <v>0.03231856841205823</v>
       </c>
       <c r="D3">
-        <v>0.03169306015084904</v>
+        <v>0.031693060150718</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.007463653780246165</v>
+        <v>0.00746365378022717</v>
       </c>
       <c r="G3">
-        <v>0.007319198832878839</v>
+        <v>0.007319198832848576</v>
       </c>
       <c r="H3">
-        <v>2.04881092492271</v>
+        <v>2.048810925117779</v>
       </c>
       <c r="I3">
-        <v>1.383392955552335</v>
+        <v>1.383392955720942</v>
       </c>
       <c r="J3">
-        <v>0.5116751132846749</v>
+        <v>0.5116751132619101</v>
       </c>
       <c r="K3">
-        <v>0.3473264055688352</v>
+        <v>0.347326405539256</v>
       </c>
       <c r="L3">
-        <v>0.5116751132846632</v>
+        <v>0.5116751132525802</v>
       </c>
       <c r="M3">
-        <v>0.3473264055688411</v>
+        <v>0.3473264055744294</v>
       </c>
       <c r="N3">
-        <v>1.054488125404451</v>
+        <v>1.054488125406114</v>
       </c>
       <c r="O3">
-        <v>1.012868503187162</v>
+        <v>1.012868503185622</v>
       </c>
       <c r="P3">
-        <v>1.064812244096948</v>
+        <v>1.064812244096026</v>
       </c>
       <c r="Q3">
-        <v>28.90285935950884</v>
+        <v>28.90285935952483</v>
       </c>
       <c r="R3">
-        <v>-89.13290661052247</v>
+        <v>-89.13290661057617</v>
       </c>
       <c r="S3">
-        <v>151.8053072097962</v>
+        <v>151.8053072099275</v>
       </c>
       <c r="T3">
-        <v>0.02854805455434508</v>
+        <v>0.0285480545538663</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -6627,22 +6627,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.05448812649741</v>
+        <v>1.054488126499496</v>
       </c>
       <c r="O4">
-        <v>1.012868506642256</v>
+        <v>1.012868506640819</v>
       </c>
       <c r="P4">
-        <v>1.064812246138461</v>
+        <v>1.064812246137029</v>
       </c>
       <c r="Q4">
-        <v>28.90285945824466</v>
+        <v>28.90285945827612</v>
       </c>
       <c r="R4">
-        <v>-89.13290652670456</v>
+        <v>-89.13290652679392</v>
       </c>
       <c r="S4">
-        <v>151.8053071885102</v>
+        <v>151.8053071886477</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -6689,22 +6689,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>1.054488126060226</v>
+        <v>1.054488126061678</v>
       </c>
       <c r="O5">
-        <v>1.012868505260219</v>
+        <v>1.012868505258116</v>
       </c>
       <c r="P5">
-        <v>1.064812245321856</v>
+        <v>1.064812245320712</v>
       </c>
       <c r="Q5">
-        <v>28.90285941875034</v>
+        <v>28.90285941877868</v>
       </c>
       <c r="R5">
-        <v>-89.1329065602317</v>
+        <v>-89.1329065602623</v>
       </c>
       <c r="S5">
-        <v>151.8053071970246</v>
+        <v>151.8053071971902</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -6823,22 +6823,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.950358162636516</v>
+        <v>0.9503581626365398</v>
       </c>
       <c r="O2">
-        <v>0.9492639078649423</v>
+        <v>0.949263907864942</v>
       </c>
       <c r="P2">
-        <v>0.9491512172441227</v>
+        <v>0.9491512172441275</v>
       </c>
       <c r="Q2">
-        <v>29.95136859201854</v>
+        <v>29.95136859201942</v>
       </c>
       <c r="R2">
-        <v>-90.094618936343</v>
+        <v>-90.0946189363426</v>
       </c>
       <c r="S2">
-        <v>149.9855933920516</v>
+        <v>149.9855933920535</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -6852,58 +6852,58 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>0.1857788844337976</v>
+        <v>0.1857788844296786</v>
       </c>
       <c r="D3">
-        <v>0.1856241055465486</v>
+        <v>0.1856241055464245</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.04290379621435694</v>
+        <v>0.0429037962134057</v>
       </c>
       <c r="G3">
-        <v>0.04286805156093708</v>
+        <v>0.04286805156090842</v>
       </c>
       <c r="H3">
-        <v>3.933564400728234</v>
+        <v>3.933564400950151</v>
       </c>
       <c r="I3">
-        <v>1.380277273631228</v>
+        <v>1.380277273778748</v>
       </c>
       <c r="J3">
-        <v>0.9822689134097025</v>
+        <v>0.982268913438333</v>
       </c>
       <c r="K3">
-        <v>0.3474656432952729</v>
+        <v>0.3474656432863268</v>
       </c>
       <c r="L3">
-        <v>0.9822689134096926</v>
+        <v>0.9822689134386264</v>
       </c>
       <c r="M3">
-        <v>0.3474656432953018</v>
+        <v>0.3474656433264189</v>
       </c>
       <c r="N3">
-        <v>0.7313310006084235</v>
+        <v>0.7313310006237299</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>0.7313310006084299</v>
+        <v>0.7313310006254859</v>
       </c>
       <c r="Q3">
-        <v>-0.01608258479789187</v>
+        <v>-0.01608258486532913</v>
       </c>
       <c r="R3">
         <v>0</v>
       </c>
       <c r="S3">
-        <v>179.9839174151944</v>
+        <v>179.9839174148756</v>
       </c>
       <c r="T3">
-        <v>0.07017346264981066</v>
+        <v>0.07017346264459953</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -6947,22 +6947,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.7313309954794257</v>
+        <v>0.7313309954953042</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.7313310180678123</v>
+        <v>0.7313310180882647</v>
       </c>
       <c r="Q4">
-        <v>-0.01607990112069938</v>
+        <v>-0.01607990107789777</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>179.9839150741862</v>
+        <v>179.9839150737142</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -7009,22 +7009,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.7313309975310243</v>
+        <v>0.7313309975461124</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0.7313310110840596</v>
+        <v>0.7313310111037852</v>
       </c>
       <c r="Q5">
-        <v>-0.0160809745915332</v>
+        <v>-0.01608097448670311</v>
       </c>
       <c r="R5">
         <v>0</v>
       </c>
       <c r="S5">
-        <v>179.9839160105895</v>
+        <v>179.983916010359</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -7268,22 +7268,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9003214985094803</v>
+        <v>0.9003214985094843</v>
       </c>
       <c r="O2">
-        <v>0.8993393732395846</v>
+        <v>0.899339373239582</v>
       </c>
       <c r="P2">
-        <v>0.8992381755753385</v>
+        <v>0.8992381755753451</v>
       </c>
       <c r="Q2">
-        <v>29.95392772300903</v>
+        <v>29.95392772300881</v>
       </c>
       <c r="R2">
-        <v>-90.08964264987587</v>
+        <v>-90.08964264987566</v>
       </c>
       <c r="S2">
-        <v>149.986347714434</v>
+        <v>149.9863477144344</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -7297,58 +7297,58 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>0.1760061738339913</v>
+        <v>0.1760061738316752</v>
       </c>
       <c r="D3">
-        <v>0.1758633179147765</v>
+        <v>0.1758633179132011</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.04064688534252217</v>
+        <v>0.04064688534198727</v>
       </c>
       <c r="G3">
-        <v>0.04061389418066496</v>
+        <v>0.04061389418030113</v>
       </c>
       <c r="H3">
-        <v>3.93355421627931</v>
+        <v>3.933554215993011</v>
       </c>
       <c r="I3">
-        <v>1.380177713395197</v>
+        <v>1.380177713283042</v>
       </c>
       <c r="J3">
-        <v>0.9822589630274553</v>
+        <v>0.9822589630576509</v>
       </c>
       <c r="K3">
-        <v>0.3473661396185401</v>
+        <v>0.3473661396055267</v>
       </c>
       <c r="L3">
-        <v>0.9822589630274428</v>
+        <v>0.9822589630228384</v>
       </c>
       <c r="M3">
-        <v>0.3473661396185643</v>
+        <v>0.3473661396117605</v>
       </c>
       <c r="N3">
-        <v>0.6928422324108532</v>
+        <v>0.6928422324115322</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>0.6928422324108552</v>
+        <v>0.6928422324137804</v>
       </c>
       <c r="Q3">
-        <v>-0.01566764921675467</v>
+        <v>-0.01566764946699842</v>
       </c>
       <c r="R3">
         <v>0</v>
       </c>
       <c r="S3">
-        <v>179.9843323507756</v>
+        <v>179.9843323504382</v>
       </c>
       <c r="T3">
-        <v>0.06648102571494606</v>
+        <v>0.06648102571716608</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -7392,22 +7392,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.6928422275519983</v>
+        <v>0.6928422275524098</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.6928422489510784</v>
+        <v>0.6928422489506281</v>
       </c>
       <c r="Q4">
-        <v>-0.01566496557836796</v>
+        <v>-0.01566496581391335</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>179.9843300097328</v>
+        <v>179.984330009336</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -7454,22 +7454,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.6928422294955399</v>
+        <v>0.6928422294960122</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0.6928422423349895</v>
+        <v>0.6928422423404434</v>
       </c>
       <c r="Q5">
-        <v>-0.01566603903368046</v>
+        <v>-0.01566603911164745</v>
       </c>
       <c r="R5">
         <v>0</v>
       </c>
       <c r="S5">
-        <v>179.9843309461499</v>
+        <v>179.9843309459008</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -7588,22 +7588,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.949974434499082</v>
+        <v>0.9499744344990871</v>
       </c>
       <c r="O2">
-        <v>0.949834137752982</v>
+        <v>0.9498341377529774</v>
       </c>
       <c r="P2">
-        <v>0.9498810489682352</v>
+        <v>0.9498810489682384</v>
       </c>
       <c r="Q2">
-        <v>29.99245213177199</v>
+        <v>29.99245213177173</v>
       </c>
       <c r="R2">
-        <v>-90.00916683746628</v>
+        <v>-90.00916683746635</v>
       </c>
       <c r="S2">
-        <v>149.9989714861777</v>
+        <v>149.9989714861781</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -7617,58 +7617,58 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>0.026890311017577</v>
+        <v>0.0268903110173998</v>
       </c>
       <c r="D3">
-        <v>0.02529585666088598</v>
+        <v>0.02529585666085731</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.006210051414373312</v>
+        <v>0.006210051414332391</v>
       </c>
       <c r="G3">
-        <v>0.005841827948067903</v>
+        <v>0.005841827948061281</v>
       </c>
       <c r="H3">
-        <v>3.933564400728234</v>
+        <v>3.933564400950151</v>
       </c>
       <c r="I3">
-        <v>1.380277273631228</v>
+        <v>1.380277273778748</v>
       </c>
       <c r="J3">
-        <v>0.9822689134097025</v>
+        <v>0.982268913438333</v>
       </c>
       <c r="K3">
-        <v>0.3474656432952729</v>
+        <v>0.3474656432863268</v>
       </c>
       <c r="L3">
-        <v>0.9822689134096926</v>
+        <v>0.9822689134386264</v>
       </c>
       <c r="M3">
-        <v>0.3474656432953018</v>
+        <v>0.3474656433264189</v>
       </c>
       <c r="N3">
-        <v>0.8820887925199997</v>
+        <v>0.8820887925191336</v>
       </c>
       <c r="O3">
-        <v>0.8371884592987457</v>
+        <v>0.8371884592972354</v>
       </c>
       <c r="P3">
-        <v>0.9154331998825589</v>
+        <v>0.9154331998861023</v>
       </c>
       <c r="Q3">
-        <v>28.92650274080131</v>
+        <v>28.92650274056746</v>
       </c>
       <c r="R3">
-        <v>-86.79307943004157</v>
+        <v>-86.79307942989828</v>
       </c>
       <c r="S3">
-        <v>153.4469752304672</v>
+        <v>153.4469752304419</v>
       </c>
       <c r="T3">
-        <v>0.02197971479326001</v>
+        <v>0.02197971479279758</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -7712,22 +7712,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8820887966711144</v>
+        <v>0.8820887966706115</v>
       </c>
       <c r="O4">
-        <v>0.8371884680777426</v>
+        <v>0.8371884680763559</v>
       </c>
       <c r="P4">
-        <v>0.9154332034574366</v>
+        <v>0.9154332034617011</v>
       </c>
       <c r="Q4">
-        <v>28.92650292340137</v>
+        <v>28.92650292316413</v>
       </c>
       <c r="R4">
-        <v>-86.79307949460488</v>
+        <v>-86.79307949442921</v>
       </c>
       <c r="S4">
-        <v>153.4469750379372</v>
+        <v>153.4469750379367</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -7774,22 +7774,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8820887950106686</v>
+        <v>0.8820887950096578</v>
       </c>
       <c r="O5">
-        <v>0.8371884645661439</v>
+        <v>0.8371884645646497</v>
       </c>
       <c r="P5">
-        <v>0.9154332020274856</v>
+        <v>0.915433202031522</v>
       </c>
       <c r="Q5">
-        <v>28.92650285036135</v>
+        <v>28.92650285013812</v>
       </c>
       <c r="R5">
-        <v>-86.79307946877957</v>
+        <v>-86.79307946858096</v>
       </c>
       <c r="S5">
-        <v>153.4469751149491</v>
+        <v>153.4469751149465</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -7908,22 +7908,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.8999770420794017</v>
+        <v>0.8999770420794047</v>
       </c>
       <c r="O2">
-        <v>0.8998511235504462</v>
+        <v>0.8998511235504446</v>
       </c>
       <c r="P2">
-        <v>0.899893226599597</v>
+        <v>0.8998932265996008</v>
       </c>
       <c r="Q2">
-        <v>29.99284932528469</v>
+        <v>29.99284932528446</v>
       </c>
       <c r="R2">
-        <v>-90.00868445213436</v>
+        <v>-90.00868445213437</v>
       </c>
       <c r="S2">
-        <v>149.9990255662928</v>
+        <v>149.9990255662929</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -7937,58 +7937,58 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>0.02547524354366063</v>
+        <v>0.02547524354365167</v>
       </c>
       <c r="D3">
-        <v>0.02396471743379126</v>
+        <v>0.02396471743389137</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.005883255574708835</v>
+        <v>0.005883255574706765</v>
       </c>
       <c r="G3">
-        <v>0.005534414507050282</v>
+        <v>0.005534414507073403</v>
       </c>
       <c r="H3">
-        <v>3.93355421627931</v>
+        <v>3.933554215993011</v>
       </c>
       <c r="I3">
-        <v>1.380177713395197</v>
+        <v>1.380177713283042</v>
       </c>
       <c r="J3">
-        <v>0.9822589630274553</v>
+        <v>0.9822589630576509</v>
       </c>
       <c r="K3">
-        <v>0.3473661396185401</v>
+        <v>0.3473661396055267</v>
       </c>
       <c r="L3">
-        <v>0.9822589630274428</v>
+        <v>0.9822589630228384</v>
       </c>
       <c r="M3">
-        <v>0.3473661396185643</v>
+        <v>0.3473661396117605</v>
       </c>
       <c r="N3">
-        <v>0.8356638298192888</v>
+        <v>0.8356638298181388</v>
       </c>
       <c r="O3">
-        <v>0.7931331858683009</v>
+        <v>0.7931331858678708</v>
       </c>
       <c r="P3">
-        <v>0.86725778095001</v>
+        <v>0.8672577809518648</v>
       </c>
       <c r="Q3">
-        <v>28.92688267422177</v>
+        <v>28.92688267404945</v>
       </c>
       <c r="R3">
-        <v>-86.79259704484494</v>
+        <v>-86.7925970447909</v>
       </c>
       <c r="S3">
-        <v>153.4470258597794</v>
+        <v>153.4470258596719</v>
       </c>
       <c r="T3">
-        <v>0.02082302977250878</v>
+        <v>0.02082302977283685</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -8032,22 +8032,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8356638337520207</v>
+        <v>0.835663833750919</v>
       </c>
       <c r="O4">
-        <v>0.7931331941849045</v>
+        <v>0.7931331941843571</v>
       </c>
       <c r="P4">
-        <v>0.867257784336395</v>
+        <v>0.8672577843376995</v>
       </c>
       <c r="Q4">
-        <v>28.92688285679296</v>
+        <v>28.92688285659513</v>
       </c>
       <c r="R4">
-        <v>-86.79259710945777</v>
+        <v>-86.79259710947248</v>
       </c>
       <c r="S4">
-        <v>153.4470256672386</v>
+        <v>153.4470256670953</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -8094,22 +8094,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.835663832178928</v>
+        <v>0.8356638321776407</v>
       </c>
       <c r="O5">
-        <v>0.7931331908582631</v>
+        <v>0.7931331908578483</v>
       </c>
       <c r="P5">
-        <v>0.8672577829818411</v>
+        <v>0.8672577829841629</v>
       </c>
       <c r="Q5">
-        <v>28.92688278376449</v>
+        <v>28.92688278360279</v>
       </c>
       <c r="R5">
-        <v>-86.79259708361263</v>
+        <v>-86.7925970835033</v>
       </c>
       <c r="S5">
-        <v>153.4470257442549</v>
+        <v>153.44702574417</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -8850,22 +8850,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.050491592260995</v>
+        <v>1.050491592261001</v>
       </c>
       <c r="O2">
-        <v>1.048173411570605</v>
+        <v>1.048173411570598</v>
       </c>
       <c r="P2">
-        <v>1.048594781003185</v>
+        <v>1.048594781003152</v>
       </c>
       <c r="Q2">
         <v>29.92695589875414</v>
       </c>
       <c r="R2">
-        <v>-90.11967249081198</v>
+        <v>-90.11967249081401</v>
       </c>
       <c r="S2">
-        <v>150.0133640543794</v>
+        <v>150.013364054379</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -8876,55 +8876,55 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>0.3396015336184986</v>
+        <v>0.3396015336196155</v>
       </c>
       <c r="D3">
-        <v>0.3396015336184985</v>
+        <v>0.3396015336196155</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.0784276159094025</v>
+        <v>0.07842761590966044</v>
       </c>
       <c r="G3">
-        <v>0.07842761590940248</v>
+        <v>0.07842761590966044</v>
       </c>
       <c r="H3">
-        <v>2.048802864003135</v>
+        <v>2.048802864167397</v>
       </c>
       <c r="I3">
-        <v>1.383313298422268</v>
+        <v>1.383313298626652</v>
       </c>
       <c r="J3">
-        <v>0.5116671529773194</v>
+        <v>0.5116671529599571</v>
       </c>
       <c r="K3">
-        <v>0.3472468026119639</v>
+        <v>0.3472468025996517</v>
       </c>
       <c r="L3">
-        <v>0.5116671529773235</v>
+        <v>0.5116671529366223</v>
       </c>
       <c r="M3">
-        <v>0.3472468026119976</v>
+        <v>0.3472468026066617</v>
       </c>
       <c r="N3">
-        <v>0.9093266326783842</v>
+        <v>0.9093266326803106</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>0.9093266326783628</v>
+        <v>0.9093266326736497</v>
       </c>
       <c r="Q3">
-        <v>8.25205865442825E-13</v>
+        <v>-4.778591225320545E-11</v>
       </c>
       <c r="R3">
         <v>0</v>
       </c>
       <c r="S3">
-        <v>179.9999999999919</v>
+        <v>-179.9999999992685</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -8968,22 +8968,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.9093266202052807</v>
+        <v>0.9093266202076929</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.9093266451514664</v>
+        <v>0.909326645144365</v>
       </c>
       <c r="Q4">
-        <v>1.163270335653725E-06</v>
+        <v>1.163178120337072E-06</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>179.9999988367224</v>
+        <v>179.9999988374205</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -9027,22 +9027,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9093266251945218</v>
+        <v>0.9093266251959025</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0.9093266401622254</v>
+        <v>0.9093266401541645</v>
       </c>
       <c r="Q5">
-        <v>6.979625413769643E-07</v>
+        <v>6.979014949868053E-07</v>
       </c>
       <c r="R5">
         <v>0</v>
       </c>
       <c r="S5">
-        <v>179.9999993020302</v>
+        <v>179.9999993029566</v>
       </c>
     </row>
   </sheetData>

--- a/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/1_four_bus_radial_1ph_grid_MP_pf_sc_results_1_bus.xlsx
+++ b/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/1_four_bus_radial_1ph_grid_MP_pf_sc_results_1_bus.xlsx
@@ -720,22 +720,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.100539455419038</v>
+        <v>1.100539455419024</v>
       </c>
       <c r="O2">
-        <v>1.097995431674429</v>
+        <v>1.097995431674444</v>
       </c>
       <c r="P2">
-        <v>1.098457996344437</v>
+        <v>1.098457996344464</v>
       </c>
       <c r="Q2">
         <v>29.92348286443664</v>
       </c>
       <c r="R2">
-        <v>-90.12536079168052</v>
+        <v>-90.12536079167887</v>
       </c>
       <c r="S2">
-        <v>150.014008153694</v>
+        <v>150.0140081536936</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -746,55 +746,55 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>0.3557435519621827</v>
+        <v>0.3557435519611505</v>
       </c>
       <c r="D3">
-        <v>0.3557435519621827</v>
+        <v>0.3557435519611505</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.0821554554193476</v>
+        <v>0.08215545541910921</v>
       </c>
       <c r="G3">
-        <v>0.08215545541934759</v>
+        <v>0.08215545541910924</v>
       </c>
       <c r="H3">
-        <v>2.048810925117779</v>
+        <v>2.04881092492271</v>
       </c>
       <c r="I3">
-        <v>1.383392955720942</v>
+        <v>1.383392955552335</v>
       </c>
       <c r="J3">
-        <v>0.5116751132619101</v>
+        <v>0.5116751132846749</v>
       </c>
       <c r="K3">
-        <v>0.347326405539256</v>
+        <v>0.3473264055688352</v>
       </c>
       <c r="L3">
-        <v>0.5116751132525802</v>
+        <v>0.5116751132846632</v>
       </c>
       <c r="M3">
-        <v>0.3473264055744294</v>
+        <v>0.3473264055688411</v>
       </c>
       <c r="N3">
-        <v>0.952627964815119</v>
+        <v>0.9526279648105369</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>0.9526279648119598</v>
+        <v>0.9526279648105332</v>
       </c>
       <c r="Q3">
-        <v>-1.011115970288249E-10</v>
+        <v>3.516126893381421E-13</v>
       </c>
       <c r="R3">
         <v>0</v>
       </c>
       <c r="S3">
-        <v>-179.9999999993845</v>
+        <v>179.9999999999924</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -838,22 +838,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.9526279517475256</v>
+        <v>0.9526279517434754</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.9526279778757328</v>
+        <v>0.9526279778775952</v>
       </c>
       <c r="Q4">
-        <v>1.163082502386709E-06</v>
+        <v>1.163269858554002E-06</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>179.9999988373277</v>
+        <v>179.9999988367229</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -897,22 +897,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.95262795697431</v>
+        <v>0.9526279569702997</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0.9526279726486904</v>
+        <v>0.9526279726507707</v>
       </c>
       <c r="Q5">
-        <v>6.978481674565027E-07</v>
+        <v>6.979620565742021E-07</v>
       </c>
       <c r="R5">
         <v>0</v>
       </c>
       <c r="S5">
-        <v>179.9999993028406</v>
+        <v>179.9999993020307</v>
       </c>
     </row>
   </sheetData>
@@ -1028,19 +1028,19 @@
         <v>1.050040203479655</v>
       </c>
       <c r="O2">
-        <v>1.049678265284738</v>
+        <v>1.049678265284739</v>
       </c>
       <c r="P2">
-        <v>1.049798862248525</v>
+        <v>1.049798862248529</v>
       </c>
       <c r="Q2">
-        <v>29.98859724152116</v>
+        <v>29.98859724152111</v>
       </c>
       <c r="R2">
-        <v>-90.01521016974888</v>
+        <v>-90.01521016974866</v>
       </c>
       <c r="S2">
-        <v>150.0038011686683</v>
+        <v>150.0038011686684</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -1051,55 +1051,55 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>0.05066945263999146</v>
+        <v>0.0506694526399671</v>
       </c>
       <c r="D3">
-        <v>0.05066945263999144</v>
+        <v>0.0506694526399671</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.01170160902292359</v>
+        <v>0.01170160902291796</v>
       </c>
       <c r="G3">
-        <v>0.01170160902292358</v>
+        <v>0.01170160902291796</v>
       </c>
       <c r="H3">
-        <v>2.048802864167397</v>
+        <v>2.048802864003135</v>
       </c>
       <c r="I3">
-        <v>1.383313298626652</v>
+        <v>1.383313298422268</v>
       </c>
       <c r="J3">
-        <v>0.5116671529599571</v>
+        <v>0.5116671529773194</v>
       </c>
       <c r="K3">
-        <v>0.3472468025996517</v>
+        <v>0.3472468026119639</v>
       </c>
       <c r="L3">
-        <v>0.5116671529366223</v>
+        <v>0.5116671529773235</v>
       </c>
       <c r="M3">
-        <v>0.3472468026066617</v>
+        <v>0.3472468026119976</v>
       </c>
       <c r="N3">
-        <v>1.002299347203896</v>
+        <v>1.002299347203498</v>
       </c>
       <c r="O3">
-        <v>0.8957178256698493</v>
+        <v>0.8957178256710512</v>
       </c>
       <c r="P3">
-        <v>1.024841978063851</v>
+        <v>1.024841978065004</v>
       </c>
       <c r="Q3">
-        <v>26.52931522749556</v>
+        <v>26.52931522749346</v>
       </c>
       <c r="R3">
-        <v>-88.39251432507884</v>
+        <v>-88.39251432502026</v>
       </c>
       <c r="S3">
-        <v>154.0981446419027</v>
+        <v>154.0981446418479</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -1143,22 +1143,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.002299347303482</v>
+        <v>1.002299347303008</v>
       </c>
       <c r="O4">
-        <v>0.8957178317805766</v>
+        <v>0.8957178317817445</v>
       </c>
       <c r="P4">
-        <v>1.02484198063662</v>
+        <v>1.024841980638074</v>
       </c>
       <c r="Q4">
-        <v>26.52931541743645</v>
+        <v>26.52931541744053</v>
       </c>
       <c r="R4">
-        <v>-88.39251415752798</v>
+        <v>-88.39251415743716</v>
       </c>
       <c r="S4">
-        <v>154.0981445242122</v>
+        <v>154.0981445241723</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -1202,22 +1202,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>1.00229934726351</v>
+        <v>1.002299347263204</v>
       </c>
       <c r="O5">
-        <v>0.8957178293357486</v>
+        <v>0.8957178293374671</v>
       </c>
       <c r="P5">
-        <v>1.02484197960712</v>
+        <v>1.024841979608846</v>
       </c>
       <c r="Q5">
-        <v>26.52931534146143</v>
+        <v>26.5293153414617</v>
       </c>
       <c r="R5">
-        <v>-88.39251422455131</v>
+        <v>-88.3925142244704</v>
       </c>
       <c r="S5">
-        <v>154.0981445713085</v>
+        <v>154.0981445712426</v>
       </c>
     </row>
   </sheetData>
@@ -1330,22 +1330,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.100044197268401</v>
+        <v>1.100044197268398</v>
       </c>
       <c r="O2">
         <v>1.099646973695688</v>
       </c>
       <c r="P2">
-        <v>1.099779330644694</v>
+        <v>1.099779330644697</v>
       </c>
       <c r="Q2">
-        <v>29.98805442002709</v>
+        <v>29.98805442002703</v>
       </c>
       <c r="R2">
-        <v>-90.01593423107225</v>
+        <v>-90.01593423107204</v>
       </c>
       <c r="S2">
-        <v>150.0039823002063</v>
+        <v>150.0039823002062</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -1356,55 +1356,55 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>0.05308151278077346</v>
+        <v>0.0530815127807549</v>
       </c>
       <c r="D3">
-        <v>0.05308151278077346</v>
+        <v>0.0530815127807549</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.01225865045985697</v>
+        <v>0.01225865045985269</v>
       </c>
       <c r="G3">
-        <v>0.01225865045985697</v>
+        <v>0.01225865045985269</v>
       </c>
       <c r="H3">
-        <v>2.048810925117779</v>
+        <v>2.04881092492271</v>
       </c>
       <c r="I3">
-        <v>1.383392955720942</v>
+        <v>1.383392955552335</v>
       </c>
       <c r="J3">
-        <v>0.5116751132619101</v>
+        <v>0.5116751132846749</v>
       </c>
       <c r="K3">
-        <v>0.347326405539256</v>
+        <v>0.3473264055688352</v>
       </c>
       <c r="L3">
-        <v>0.5116751132525802</v>
+        <v>0.5116751132846632</v>
       </c>
       <c r="M3">
-        <v>0.3473264055744294</v>
+        <v>0.3473264055688411</v>
       </c>
       <c r="N3">
-        <v>1.050030450406209</v>
+        <v>1.050030450405306</v>
       </c>
       <c r="O3">
-        <v>0.9383574270889607</v>
+        <v>0.9383574270901905</v>
       </c>
       <c r="P3">
-        <v>1.073635628314516</v>
+        <v>1.073635628315036</v>
       </c>
       <c r="Q3">
-        <v>26.52884014036632</v>
+        <v>26.52884014038561</v>
       </c>
       <c r="R3">
-        <v>-88.39323838626153</v>
+        <v>-88.3932383862076</v>
       </c>
       <c r="S3">
-        <v>154.0983225150189</v>
+        <v>154.0983225149558</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -1448,22 +1448,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.05003045051003</v>
+        <v>1.050030450509231</v>
       </c>
       <c r="O4">
-        <v>0.9383574334906466</v>
+        <v>0.9383574334920346</v>
       </c>
       <c r="P4">
-        <v>1.073635631010053</v>
+        <v>1.073635631011002</v>
       </c>
       <c r="Q4">
-        <v>26.52884033031895</v>
+        <v>26.52884033034576</v>
       </c>
       <c r="R4">
-        <v>-88.39323821865327</v>
+        <v>-88.39323821857178</v>
       </c>
       <c r="S4">
-        <v>154.098322397334</v>
+        <v>154.0983223972833</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -1507,22 +1507,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>1.050030450468467</v>
+        <v>1.050030450467661</v>
       </c>
       <c r="O5">
-        <v>0.9383574309295261</v>
+        <v>0.938357430931297</v>
       </c>
       <c r="P5">
-        <v>1.073635629931496</v>
+        <v>1.073635629932615</v>
       </c>
       <c r="Q5">
-        <v>26.52884025434003</v>
+        <v>26.5288402543617</v>
       </c>
       <c r="R5">
-        <v>-88.39323828570238</v>
+        <v>-88.39323828562611</v>
       </c>
       <c r="S5">
-        <v>154.0983224444265</v>
+        <v>154.0983224443523</v>
       </c>
     </row>
   </sheetData>
@@ -1635,22 +1635,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9504947120678335</v>
+        <v>0.9504947120678211</v>
       </c>
       <c r="O2">
-        <v>0.9492639078649426</v>
+        <v>0.9492639078649421</v>
       </c>
       <c r="P2">
-        <v>0.9491368456360528</v>
+        <v>0.9491368456360405</v>
       </c>
       <c r="Q2">
-        <v>29.95712896109875</v>
+        <v>29.95712896109838</v>
       </c>
       <c r="R2">
-        <v>-90.09461893634224</v>
+        <v>-90.094618936343</v>
       </c>
       <c r="S2">
-        <v>149.9956165875561</v>
+        <v>149.9956165875549</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -1661,55 +1661,55 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>0.1823567177678155</v>
+        <v>0.1823567177694458</v>
       </c>
       <c r="D3">
-        <v>0.1823567177678155</v>
+        <v>0.1823567177694458</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.04211348066425372</v>
+        <v>0.04211348066463021</v>
       </c>
       <c r="G3">
-        <v>0.04211348066425372</v>
+        <v>0.04211348066463021</v>
       </c>
       <c r="H3">
-        <v>3.933564400950151</v>
+        <v>3.933564400728234</v>
       </c>
       <c r="I3">
-        <v>1.380277273778748</v>
+        <v>1.380277273631228</v>
       </c>
       <c r="J3">
-        <v>0.982268913438333</v>
+        <v>0.9822689134097025</v>
       </c>
       <c r="K3">
-        <v>0.3474656432863268</v>
+        <v>0.3474656432952729</v>
       </c>
       <c r="L3">
-        <v>0.9822689134386264</v>
+        <v>0.9822689134096926</v>
       </c>
       <c r="M3">
-        <v>0.3474656433264189</v>
+        <v>0.3474656432953018</v>
       </c>
       <c r="N3">
-        <v>0.8227241232789595</v>
+        <v>0.8227241232713736</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>0.8227241232815777</v>
+        <v>0.8227241232713804</v>
       </c>
       <c r="Q3">
-        <v>-7.916419987117949E-11</v>
+        <v>8.244371258761251E-14</v>
       </c>
       <c r="R3">
         <v>0</v>
       </c>
       <c r="S3">
-        <v>179.9999999994634</v>
+        <v>179.9999999999926</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -1753,22 +1753,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8227241119946079</v>
+        <v>0.8227241119861857</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.8227241345691217</v>
+        <v>0.8227241345565697</v>
       </c>
       <c r="Q4">
-        <v>2.233461245772163E-06</v>
+        <v>2.233477443745994E-06</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>179.9999977657683</v>
+        <v>179.9999977665153</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -1812,22 +1812,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8227241165080402</v>
+        <v>0.8227241165002603</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0.8227241300542772</v>
+        <v>0.8227241300424942</v>
       </c>
       <c r="Q5">
-        <v>1.340102594598777E-06</v>
+        <v>1.34008652936944E-06</v>
       </c>
       <c r="R5">
         <v>0</v>
       </c>
       <c r="S5">
-        <v>179.9999986593054</v>
+        <v>179.9999986599062</v>
       </c>
     </row>
   </sheetData>
@@ -1940,22 +1940,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9004440553540254</v>
+        <v>0.9004440553540198</v>
       </c>
       <c r="O2">
-        <v>0.8993393732395796</v>
+        <v>0.8993393732395855</v>
       </c>
       <c r="P2">
-        <v>0.8992252737407059</v>
+        <v>0.899225273740702</v>
       </c>
       <c r="Q2">
-        <v>29.95938501571742</v>
+        <v>29.95938501571753</v>
       </c>
       <c r="R2">
-        <v>-90.08964264987569</v>
+        <v>-90.08964264987587</v>
       </c>
       <c r="S2">
-        <v>149.9958430352665</v>
+        <v>149.9958430352658</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -1966,55 +1966,55 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>0.1727660505194399</v>
+        <v>0.1727660505215357</v>
       </c>
       <c r="D3">
-        <v>0.1727660505194399</v>
+        <v>0.1727660505215357</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.03989861090422646</v>
+        <v>0.03989861090471049</v>
       </c>
       <c r="G3">
-        <v>0.03989861090422646</v>
+        <v>0.03989861090471049</v>
       </c>
       <c r="H3">
-        <v>3.933554215993011</v>
+        <v>3.93355421627931</v>
       </c>
       <c r="I3">
-        <v>1.380177713283042</v>
+        <v>1.380177713395197</v>
       </c>
       <c r="J3">
-        <v>0.9822589630576509</v>
+        <v>0.9822589630274553</v>
       </c>
       <c r="K3">
-        <v>0.3473661396055267</v>
+        <v>0.3473661396185401</v>
       </c>
       <c r="L3">
-        <v>0.9822589630228384</v>
+        <v>0.9822589630274428</v>
       </c>
       <c r="M3">
-        <v>0.3473661396117605</v>
+        <v>0.3473661396185643</v>
       </c>
       <c r="N3">
-        <v>0.7794228427603641</v>
+        <v>0.7794228427583269</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>0.7794228427641845</v>
+        <v>0.7794228427583302</v>
       </c>
       <c r="Q3">
-        <v>-1.953886823464652E-10</v>
+        <v>3.469473728784693E-14</v>
       </c>
       <c r="R3">
         <v>0</v>
       </c>
       <c r="S3">
-        <v>179.9999999997936</v>
+        <v>179.9999999999927</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -2058,22 +2058,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.7794228320685856</v>
+        <v>0.7794228320670965</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.7794228534551485</v>
+        <v>0.7794228534495617</v>
       </c>
       <c r="Q4">
-        <v>2.233310358015714E-06</v>
+        <v>2.233477400849885E-06</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>179.9999977662947</v>
+        <v>179.9999977665154</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -2117,22 +2117,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.7794228363458089</v>
+        <v>0.7794228363435881</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0.7794228491804261</v>
+        <v>0.7794228491730694</v>
       </c>
       <c r="Q5">
-        <v>1.339986384842014E-06</v>
+        <v>1.340086485672968E-06</v>
       </c>
       <c r="R5">
         <v>0</v>
       </c>
       <c r="S5">
-        <v>179.9999986596357</v>
+        <v>179.9999986599062</v>
       </c>
     </row>
   </sheetData>
@@ -2245,22 +2245,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9500519910672208</v>
+        <v>0.9500519910672174</v>
       </c>
       <c r="O2">
-        <v>0.9497163730518657</v>
+        <v>0.9497163730518684</v>
       </c>
       <c r="P2">
-        <v>0.9498061775520101</v>
+        <v>0.9498061775520078</v>
       </c>
       <c r="Q2">
-        <v>29.98831337242362</v>
+        <v>29.9883133724237</v>
       </c>
       <c r="R2">
-        <v>-90.0171226675338</v>
+        <v>-90.01712266753385</v>
       </c>
       <c r="S2">
-        <v>150.00312912787</v>
+        <v>150.0031291278697</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -2271,55 +2271,55 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>0.0422386439613798</v>
+        <v>0.04223864396144971</v>
       </c>
       <c r="D3">
-        <v>0.04223864396137981</v>
+        <v>0.04223864396144972</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.009754597129877779</v>
+        <v>0.009754597129893924</v>
       </c>
       <c r="G3">
-        <v>0.009754597129877781</v>
+        <v>0.009754597129893926</v>
       </c>
       <c r="H3">
-        <v>3.933564400950151</v>
+        <v>3.933564400728234</v>
       </c>
       <c r="I3">
-        <v>1.380277273778748</v>
+        <v>1.380277273631228</v>
       </c>
       <c r="J3">
-        <v>0.982268913438333</v>
+        <v>0.9822689134097025</v>
       </c>
       <c r="K3">
-        <v>0.3474656432863268</v>
+        <v>0.3474656432952729</v>
       </c>
       <c r="L3">
-        <v>0.9822689134386264</v>
+        <v>0.9822689134096926</v>
       </c>
       <c r="M3">
-        <v>0.3474656433264189</v>
+        <v>0.3474656432953018</v>
       </c>
       <c r="N3">
-        <v>0.8688824565889276</v>
+        <v>0.8688824565885807</v>
       </c>
       <c r="O3">
-        <v>0.7466807782052592</v>
+        <v>0.7466807782052226</v>
       </c>
       <c r="P3">
-        <v>0.9367813698693714</v>
+        <v>0.9367813698662649</v>
       </c>
       <c r="Q3">
-        <v>25.3111727077902</v>
+        <v>25.31117270792592</v>
       </c>
       <c r="R3">
-        <v>-84.27300812653813</v>
+        <v>-84.27300812665352</v>
       </c>
       <c r="S3">
-        <v>156.6375696710193</v>
+        <v>156.6375696710438</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -2363,22 +2363,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8688824600066826</v>
+        <v>0.868882460005816</v>
       </c>
       <c r="O4">
-        <v>0.7466807938660103</v>
+        <v>0.7466807938650381</v>
       </c>
       <c r="P4">
-        <v>0.9367813729419699</v>
+        <v>0.9367813729377028</v>
       </c>
       <c r="Q4">
-        <v>25.31117317563863</v>
+        <v>25.31117317577862</v>
       </c>
       <c r="R4">
-        <v>-84.27300825563718</v>
+        <v>-84.27300825578014</v>
       </c>
       <c r="S4">
-        <v>156.6375692274932</v>
+        <v>156.6375692275357</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -2422,22 +2422,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8688824586392562</v>
+        <v>0.8688824586389218</v>
       </c>
       <c r="O5">
-        <v>0.746680787601851</v>
+        <v>0.7466807876011122</v>
       </c>
       <c r="P5">
-        <v>0.9367813717127048</v>
+        <v>0.9367813717091278</v>
       </c>
       <c r="Q5">
-        <v>25.31117298852318</v>
+        <v>25.31117298863755</v>
       </c>
       <c r="R5">
-        <v>-84.27300820398068</v>
+        <v>-84.27300820412948</v>
       </c>
       <c r="S5">
-        <v>156.6375694049024</v>
+        <v>156.6375694049389</v>
       </c>
     </row>
   </sheetData>
@@ -2550,22 +2550,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9000466517344065</v>
+        <v>0.9000466517344052</v>
       </c>
       <c r="O2">
-        <v>0.8997454277137936</v>
+        <v>0.8997454277137985</v>
       </c>
       <c r="P2">
-        <v>0.8998260263376505</v>
+        <v>0.8998260263376501</v>
       </c>
       <c r="Q2">
-        <v>29.98892829893984</v>
+        <v>29.98892829894006</v>
       </c>
       <c r="R2">
-        <v>-90.01622172940525</v>
+        <v>-90.0162217294052</v>
       </c>
       <c r="S2">
-        <v>150.0029642775244</v>
+        <v>150.0029642775241</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -2576,55 +2576,55 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>0.04001618573223596</v>
+        <v>0.04001618573231812</v>
       </c>
       <c r="D3">
-        <v>0.04001618573223596</v>
+        <v>0.0400161857323181</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.009241342379486128</v>
+        <v>0.009241342379505101</v>
       </c>
       <c r="G3">
-        <v>0.009241342379486128</v>
+        <v>0.009241342379505099</v>
       </c>
       <c r="H3">
-        <v>3.933554215993011</v>
+        <v>3.93355421627931</v>
       </c>
       <c r="I3">
-        <v>1.380177713283042</v>
+        <v>1.380177713395197</v>
       </c>
       <c r="J3">
-        <v>0.9822589630576509</v>
+        <v>0.9822589630274553</v>
       </c>
       <c r="K3">
-        <v>0.3473661396055267</v>
+        <v>0.3473661396185401</v>
       </c>
       <c r="L3">
-        <v>0.9822589630228384</v>
+        <v>0.9822589630274428</v>
       </c>
       <c r="M3">
-        <v>0.3473661396117605</v>
+        <v>0.3473661396185643</v>
       </c>
       <c r="N3">
-        <v>0.823148412720813</v>
+        <v>0.8231484127221256</v>
       </c>
       <c r="O3">
-        <v>0.7073928966712167</v>
+        <v>0.7073928966725872</v>
       </c>
       <c r="P3">
-        <v>0.8874846372725484</v>
+        <v>0.8874846372706626</v>
       </c>
       <c r="Q3">
-        <v>25.31166697421952</v>
+        <v>25.31166697432942</v>
       </c>
       <c r="R3">
-        <v>-84.27210718856466</v>
+        <v>-84.27210718877164</v>
       </c>
       <c r="S3">
-        <v>156.6374306579122</v>
+        <v>156.6374306578857</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -2668,22 +2668,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8231484159587104</v>
+        <v>0.8231484159599609</v>
       </c>
       <c r="O4">
-        <v>0.7073929115064023</v>
+        <v>0.7073929115076905</v>
       </c>
       <c r="P4">
-        <v>0.8874846401820266</v>
+        <v>0.887484640179901</v>
       </c>
       <c r="Q4">
-        <v>25.31166744203546</v>
+        <v>25.31166744215431</v>
       </c>
       <c r="R4">
-        <v>-84.27210731778459</v>
+        <v>-84.27210731799734</v>
       </c>
       <c r="S4">
-        <v>156.6374302144013</v>
+        <v>156.6374302143796</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -2727,22 +2727,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8231484146635023</v>
+        <v>0.8231484146648267</v>
       </c>
       <c r="O5">
-        <v>0.7073929055729441</v>
+        <v>0.7073929055736495</v>
       </c>
       <c r="P5">
-        <v>0.8874846390185372</v>
+        <v>0.8874846390162058</v>
       </c>
       <c r="Q5">
-        <v>25.31166725493582</v>
+        <v>25.31166725502436</v>
       </c>
       <c r="R5">
-        <v>-84.27210726606666</v>
+        <v>-84.27210726630706</v>
       </c>
       <c r="S5">
-        <v>156.6374303917965</v>
+        <v>156.637430391782</v>
       </c>
     </row>
   </sheetData>
@@ -2858,22 +2858,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.049226942770166</v>
+        <v>1.049226942770095</v>
       </c>
       <c r="O2">
-        <v>1.049999952316288</v>
+        <v>1.04999995231628</v>
       </c>
       <c r="P2">
-        <v>1.049860293027526</v>
+        <v>1.049860293027453</v>
       </c>
       <c r="Q2">
-        <v>29.98445362311615</v>
+        <v>29.98445362311656</v>
       </c>
       <c r="R2">
-        <v>-89.99999999999464</v>
+        <v>-89.99999999999635</v>
       </c>
       <c r="S2">
-        <v>149.9556948814907</v>
+        <v>149.9556948814871</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -2884,7 +2884,7 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>0.1961438699686732</v>
+        <v>0.1961438699816457</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -2893,7 +2893,7 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0.04529748712550851</v>
+        <v>0.04529748712850438</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -2902,43 +2902,43 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>2.048802864200902</v>
+        <v>2.048802864003164</v>
       </c>
       <c r="I3">
-        <v>1.383313298496587</v>
+        <v>1.38331329842227</v>
       </c>
       <c r="J3">
-        <v>0.5116671529789214</v>
+        <v>0.5116671529774101</v>
       </c>
       <c r="K3">
-        <v>0.3472468026224648</v>
+        <v>0.3472468026119749</v>
       </c>
       <c r="L3">
-        <v>0.511667152990275</v>
+        <v>0.5116671529773953</v>
       </c>
       <c r="M3">
-        <v>0.3472468026513886</v>
+        <v>0.347246802612</v>
       </c>
       <c r="N3">
-        <v>0.8015481718556675</v>
+        <v>0.8015481718455055</v>
       </c>
       <c r="O3">
-        <v>1.049999952327208</v>
+        <v>1.049999952316279</v>
       </c>
       <c r="P3">
-        <v>0.8021790979654234</v>
+        <v>0.8021790979292637</v>
       </c>
       <c r="Q3">
-        <v>40.87275499113137</v>
+        <v>40.87275499285191</v>
       </c>
       <c r="R3">
-        <v>-89.9999999997267</v>
+        <v>-89.99999999999589</v>
       </c>
       <c r="S3">
-        <v>139.0751989925501</v>
+        <v>139.0751989924359</v>
       </c>
       <c r="T3">
-        <v>0.1961438699686732</v>
+        <v>0.1961438699816457</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -2982,22 +2982,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8015481846347969</v>
+        <v>0.8015481846251941</v>
       </c>
       <c r="O4">
-        <v>1.049999952322287</v>
+        <v>1.049999952316279</v>
       </c>
       <c r="P4">
-        <v>0.8021791012856709</v>
+        <v>0.8021791012470415</v>
       </c>
       <c r="Q4">
-        <v>40.87275488314362</v>
+        <v>40.87275488491994</v>
       </c>
       <c r="R4">
-        <v>-89.99999999936554</v>
+        <v>-89.99999999999588</v>
       </c>
       <c r="S4">
-        <v>139.0751998811449</v>
+        <v>139.075199880503</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -3044,22 +3044,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8015481795234034</v>
+        <v>0.8015481795133188</v>
       </c>
       <c r="O5">
-        <v>1.049999952328854</v>
+        <v>1.049999952316279</v>
       </c>
       <c r="P5">
-        <v>0.8021790999560043</v>
+        <v>0.8021790999199303</v>
       </c>
       <c r="Q5">
-        <v>40.87275492625946</v>
+        <v>40.87275492809272</v>
       </c>
       <c r="R5">
-        <v>-89.99999999992271</v>
+        <v>-89.99999999999589</v>
       </c>
       <c r="S5">
-        <v>139.0751995251119</v>
+        <v>139.0751995252762</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -3178,22 +3178,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.099151663052062</v>
+        <v>1.099151663051994</v>
       </c>
       <c r="O2">
-        <v>1.100000023841856</v>
+        <v>1.100000023841853</v>
       </c>
       <c r="P2">
-        <v>1.099846725405492</v>
+        <v>1.099846725405407</v>
       </c>
       <c r="Q2">
-        <v>29.98371562225271</v>
+        <v>29.98371562225426</v>
       </c>
       <c r="R2">
-        <v>-89.99999999999493</v>
+        <v>-89.99999999999635</v>
       </c>
       <c r="S2">
-        <v>149.9535871398364</v>
+        <v>149.9535871398336</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -3204,7 +3204,7 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>0.2054755533864972</v>
+        <v>0.2054755534008091</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0.04745254713093064</v>
+        <v>0.04745254713423582</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -3222,43 +3222,43 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>2.048810925143179</v>
+        <v>2.048810924922739</v>
       </c>
       <c r="I3">
-        <v>1.383392955596281</v>
+        <v>1.383392955552338</v>
       </c>
       <c r="J3">
-        <v>0.511675113301345</v>
+        <v>0.5116751132847441</v>
       </c>
       <c r="K3">
-        <v>0.3473264055908857</v>
+        <v>0.3473264055688183</v>
       </c>
       <c r="L3">
-        <v>0.511675113291863</v>
+        <v>0.5116751132847353</v>
       </c>
       <c r="M3">
-        <v>0.3473264056029481</v>
+        <v>0.3473264055688434</v>
       </c>
       <c r="N3">
-        <v>0.8396969228516016</v>
+        <v>0.8396969228492067</v>
       </c>
       <c r="O3">
-        <v>1.100000023850102</v>
+        <v>1.100000023841853</v>
       </c>
       <c r="P3">
-        <v>0.8403785429975333</v>
+        <v>0.8403785429622926</v>
       </c>
       <c r="Q3">
-        <v>40.87252920861007</v>
+        <v>40.87252921037393</v>
       </c>
       <c r="R3">
-        <v>-89.99999999972637</v>
+        <v>-89.99999999999589</v>
       </c>
       <c r="S3">
-        <v>139.0737992407105</v>
+        <v>139.0737992409941</v>
       </c>
       <c r="T3">
-        <v>0.2054755533864972</v>
+        <v>0.2054755534008091</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -3302,22 +3302,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8396969362384613</v>
+        <v>0.8396969362380932</v>
       </c>
       <c r="O4">
-        <v>1.100000023848318</v>
+        <v>1.100000023841853</v>
       </c>
       <c r="P4">
-        <v>0.8403785464739125</v>
+        <v>0.8403785464372405</v>
       </c>
       <c r="Q4">
-        <v>40.87252910067588</v>
+        <v>40.87252910248374</v>
       </c>
       <c r="R4">
-        <v>-89.9999999995712</v>
+        <v>-89.99999999999589</v>
       </c>
       <c r="S4">
-        <v>139.0738001289134</v>
+        <v>139.0738001291151</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -3364,22 +3364,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8396969308848526</v>
+        <v>0.8396969308825385</v>
       </c>
       <c r="O5">
-        <v>1.100000023851826</v>
+        <v>1.100000023841853</v>
       </c>
       <c r="P5">
-        <v>0.8403785450824125</v>
+        <v>0.8403785450472612</v>
       </c>
       <c r="Q5">
-        <v>40.87252914376322</v>
+        <v>40.87252914563982</v>
       </c>
       <c r="R5">
-        <v>-89.99999999992238</v>
+        <v>-89.99999999999589</v>
       </c>
       <c r="S5">
-        <v>139.0737997733047</v>
+        <v>139.0737997738667</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -3498,22 +3498,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.0498792949505</v>
+        <v>1.049879294950495</v>
       </c>
       <c r="O2">
-        <v>1.049999952316286</v>
+        <v>1.049999952316284</v>
       </c>
       <c r="P2">
-        <v>1.049959770497431</v>
+        <v>1.049959770497422</v>
       </c>
       <c r="Q2">
-        <v>29.99873081648531</v>
+        <v>29.99873081648546</v>
       </c>
       <c r="R2">
-        <v>-89.99999999999609</v>
+        <v>-89.99999999999635</v>
       </c>
       <c r="S2">
-        <v>149.9936633497472</v>
+        <v>149.993663349747</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -3524,7 +3524,7 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>0.02925678275235446</v>
+        <v>0.02925678275263625</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -3533,7 +3533,7 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0.006756564659758357</v>
+        <v>0.006756564659823432</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -3542,43 +3542,43 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>2.048802864200902</v>
+        <v>2.048802864003164</v>
       </c>
       <c r="I3">
-        <v>1.383313298496587</v>
+        <v>1.38331329842227</v>
       </c>
       <c r="J3">
-        <v>0.5116671529789214</v>
+        <v>0.5116671529774101</v>
       </c>
       <c r="K3">
-        <v>0.3472468026224648</v>
+        <v>0.3472468026119749</v>
       </c>
       <c r="L3">
-        <v>0.511667152990275</v>
+        <v>0.5116671529773953</v>
       </c>
       <c r="M3">
-        <v>0.3472468026513886</v>
+        <v>0.347246802612</v>
       </c>
       <c r="N3">
-        <v>1.015361077963079</v>
+        <v>1.015361077962755</v>
       </c>
       <c r="O3">
-        <v>1.049999952318143</v>
+        <v>1.049999952316284</v>
       </c>
       <c r="P3">
-        <v>1.007841946614584</v>
+        <v>1.007841946611173</v>
       </c>
       <c r="Q3">
-        <v>31.61386361979187</v>
+        <v>31.61386361990858</v>
       </c>
       <c r="R3">
-        <v>-89.99999999996629</v>
+        <v>-89.99999999999629</v>
       </c>
       <c r="S3">
-        <v>149.0875829959597</v>
+        <v>149.0875829960723</v>
       </c>
       <c r="T3">
-        <v>0.02925678275235446</v>
+        <v>0.02925678275263625</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -3622,22 +3622,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.015361079869085</v>
+        <v>1.015361079868778</v>
       </c>
       <c r="O4">
-        <v>1.049999952317413</v>
+        <v>1.049999952316284</v>
       </c>
       <c r="P4">
-        <v>1.007841947695765</v>
+        <v>1.007841947691761</v>
       </c>
       <c r="Q4">
-        <v>31.61386360698439</v>
+        <v>31.61386360710813</v>
       </c>
       <c r="R4">
-        <v>-89.99999999991128</v>
+        <v>-89.99999999999629</v>
       </c>
       <c r="S4">
-        <v>149.0875830862083</v>
+        <v>149.08758308626</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -3684,22 +3684,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>1.015361079106823</v>
+        <v>1.015361079106369</v>
       </c>
       <c r="O5">
-        <v>1.049999952318433</v>
+        <v>1.049999952316284</v>
       </c>
       <c r="P5">
-        <v>1.007841947262916</v>
+        <v>1.007841947259526</v>
       </c>
       <c r="Q5">
-        <v>31.61386361209446</v>
+        <v>31.61386361222831</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999808</v>
+        <v>-89.99999999999629</v>
       </c>
       <c r="S5">
-        <v>149.0875830500398</v>
+        <v>149.0875830501849</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -3943,22 +3943,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.099867602508715</v>
+        <v>1.099867602508712</v>
       </c>
       <c r="O2">
-        <v>1.100000023841858</v>
+        <v>1.100000023841857</v>
       </c>
       <c r="P2">
-        <v>1.099955923916915</v>
+        <v>1.099955923916905</v>
       </c>
       <c r="Q2">
-        <v>29.99867042519972</v>
+        <v>29.99867042519999</v>
       </c>
       <c r="R2">
-        <v>-89.99999999999609</v>
+        <v>-89.99999999999635</v>
       </c>
       <c r="S2">
-        <v>149.9933616553706</v>
+        <v>149.9933616553705</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -3969,7 +3969,7 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>0.03064974122551201</v>
+        <v>0.03064974122581553</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -3978,7 +3978,7 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0.007078254644330904</v>
+        <v>0.007078254644401</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -3987,43 +3987,43 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>2.048810925143179</v>
+        <v>2.048810924922739</v>
       </c>
       <c r="I3">
-        <v>1.383392955596281</v>
+        <v>1.383392955552338</v>
       </c>
       <c r="J3">
-        <v>0.511675113301345</v>
+        <v>0.5116751132847441</v>
       </c>
       <c r="K3">
-        <v>0.3473264055908857</v>
+        <v>0.3473264055688183</v>
       </c>
       <c r="L3">
-        <v>0.511675113291863</v>
+        <v>0.5116751132847353</v>
       </c>
       <c r="M3">
-        <v>0.3473264056029481</v>
+        <v>0.3473264055688434</v>
       </c>
       <c r="N3">
-        <v>1.06370608486281</v>
+        <v>1.063706084863743</v>
       </c>
       <c r="O3">
-        <v>1.100000023843486</v>
+        <v>1.100000023841857</v>
       </c>
       <c r="P3">
-        <v>1.055832789379671</v>
+        <v>1.055832789376986</v>
       </c>
       <c r="Q3">
-        <v>31.6138103102302</v>
+        <v>31.61381031032723</v>
       </c>
       <c r="R3">
-        <v>-89.99999999995501</v>
+        <v>-89.99999999999629</v>
       </c>
       <c r="S3">
-        <v>149.0872889870731</v>
+        <v>149.0872889872169</v>
       </c>
       <c r="T3">
-        <v>0.03064974122551201</v>
+        <v>0.03064974122581553</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -4067,22 +4067,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.06370608685952</v>
+        <v>1.063706086860703</v>
       </c>
       <c r="O4">
-        <v>1.100000023843223</v>
+        <v>1.100000023841857</v>
       </c>
       <c r="P4">
-        <v>1.055832790511858</v>
+        <v>1.055832790508953</v>
       </c>
       <c r="Q4">
-        <v>31.61381029743312</v>
+        <v>31.61381029753585</v>
       </c>
       <c r="R4">
-        <v>-89.9999999999321</v>
+        <v>-89.99999999999629</v>
       </c>
       <c r="S4">
-        <v>149.0872890772836</v>
+        <v>149.0872890774176</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -4129,22 +4129,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>1.063706086061123</v>
+        <v>1.063706086061919</v>
       </c>
       <c r="O5">
-        <v>1.10000002384379</v>
+        <v>1.100000023841857</v>
       </c>
       <c r="P5">
-        <v>1.055832790058829</v>
+        <v>1.055832790056166</v>
       </c>
       <c r="Q5">
-        <v>31.6138103025382</v>
+        <v>31.6138103026524</v>
       </c>
       <c r="R5">
-        <v>-89.99999999998681</v>
+        <v>-89.99999999999629</v>
       </c>
       <c r="S5">
-        <v>149.0872890411609</v>
+        <v>149.0872890413373</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -4263,22 +4263,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9495899703454814</v>
+        <v>0.9495899703454644</v>
       </c>
       <c r="O2">
-        <v>0.9499999880790841</v>
+        <v>0.9499999880790715</v>
       </c>
       <c r="P2">
-        <v>0.9500428745733545</v>
+        <v>0.9500428745733643</v>
       </c>
       <c r="Q2">
-        <v>29.98273632820589</v>
+        <v>29.98273632820458</v>
       </c>
       <c r="R2">
-        <v>-89.99999999999676</v>
+        <v>-89.99999999999635</v>
       </c>
       <c r="S2">
-        <v>149.9699552917316</v>
+        <v>149.9699552917309</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -4289,7 +4289,7 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>0.1052661192970085</v>
+        <v>0.1052661193026717</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -4298,7 +4298,7 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0.0243101692873198</v>
+        <v>0.02431016928862766</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -4307,43 +4307,43 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>3.933564400979036</v>
+        <v>3.933564400728284</v>
       </c>
       <c r="I3">
-        <v>1.380277273848993</v>
+        <v>1.38027727363123</v>
       </c>
       <c r="J3">
-        <v>0.9822689134123498</v>
+        <v>0.982268913409819</v>
       </c>
       <c r="K3">
-        <v>0.3474656433491256</v>
+        <v>0.347465643295257</v>
       </c>
       <c r="L3">
-        <v>0.9822689134193464</v>
+        <v>0.9822689134098265</v>
       </c>
       <c r="M3">
-        <v>0.3474656432902385</v>
+        <v>0.347465643295304</v>
       </c>
       <c r="N3">
-        <v>0.7253070805946787</v>
+        <v>0.7253070805808111</v>
       </c>
       <c r="O3">
-        <v>0.9499999880786806</v>
+        <v>0.9499999880790715</v>
       </c>
       <c r="P3">
-        <v>0.725911863148752</v>
+        <v>0.725911863146719</v>
       </c>
       <c r="Q3">
-        <v>40.86342210820997</v>
+        <v>40.86342210870047</v>
       </c>
       <c r="R3">
-        <v>-90.00000000046191</v>
+        <v>-89.99999999999589</v>
       </c>
       <c r="S3">
-        <v>139.0814304934232</v>
+        <v>139.0814304927861</v>
       </c>
       <c r="T3">
-        <v>0.1052661192970085</v>
+        <v>0.1052661193026717</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -4387,22 +4387,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.7253070988706876</v>
+        <v>0.7253070988559559</v>
       </c>
       <c r="O4">
-        <v>0.9499999880793276</v>
+        <v>0.9499999880790715</v>
       </c>
       <c r="P4">
-        <v>0.725911872841378</v>
+        <v>0.7259118728404218</v>
       </c>
       <c r="Q4">
-        <v>40.86342154295953</v>
+        <v>40.86342154349578</v>
       </c>
       <c r="R4">
-        <v>-90.00000000063727</v>
+        <v>-89.99999999999589</v>
       </c>
       <c r="S4">
-        <v>139.0814318402062</v>
+        <v>139.081431839697</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -4449,22 +4449,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.7253070915609069</v>
+        <v>0.7253070915458983</v>
       </c>
       <c r="O5">
-        <v>0.9499999880813121</v>
+        <v>0.9499999880790715</v>
       </c>
       <c r="P5">
-        <v>0.7259118689648881</v>
+        <v>0.7259118689629408</v>
       </c>
       <c r="Q5">
-        <v>40.8634217688844</v>
+        <v>40.86342176957764</v>
       </c>
       <c r="R5">
-        <v>-90.00000000082207</v>
+        <v>-89.99999999999589</v>
       </c>
       <c r="S5">
-        <v>139.0814313011643</v>
+        <v>139.0814313009327</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -4583,22 +4583,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.8996319840317428</v>
+        <v>0.8996319840317653</v>
       </c>
       <c r="O2">
-        <v>0.8999999761581369</v>
+        <v>0.8999999761581394</v>
       </c>
       <c r="P2">
-        <v>0.9000384811266734</v>
+        <v>0.9000384811266839</v>
       </c>
       <c r="Q2">
-        <v>29.98364396239858</v>
+        <v>29.98364396239909</v>
       </c>
       <c r="R2">
-        <v>-89.9999999999967</v>
+        <v>-89.99999999999635</v>
       </c>
       <c r="S2">
-        <v>149.971536050996</v>
+        <v>149.9715360509975</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -4609,7 +4609,7 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>0.09972782896751022</v>
+        <v>0.0997278289626669</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -4618,7 +4618,7 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0.02303115590322656</v>
+        <v>0.02303115590210804</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -4627,43 +4627,43 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>3.933554215957431</v>
+        <v>3.933554216279361</v>
       </c>
       <c r="I3">
-        <v>1.380177713378632</v>
+        <v>1.380177713395198</v>
       </c>
       <c r="J3">
-        <v>0.9822589630197631</v>
+        <v>0.9822589630275964</v>
       </c>
       <c r="K3">
-        <v>0.3473661396591991</v>
+        <v>0.3473661396185194</v>
       </c>
       <c r="L3">
-        <v>0.9822589630179832</v>
+        <v>0.9822589630275768</v>
       </c>
       <c r="M3">
-        <v>0.3473661396440931</v>
+        <v>0.3473661396185667</v>
       </c>
       <c r="N3">
-        <v>0.687144402035396</v>
+        <v>0.687144402043</v>
       </c>
       <c r="O3">
-        <v>0.8999999761546016</v>
+        <v>0.8999999761581394</v>
       </c>
       <c r="P3">
-        <v>0.6877025778113849</v>
+        <v>0.6877025778260556</v>
       </c>
       <c r="Q3">
-        <v>40.86384470287376</v>
+        <v>40.86384470191874</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999007</v>
+        <v>-89.99999999999589</v>
       </c>
       <c r="S3">
-        <v>139.0824298862344</v>
+        <v>139.0824298864973</v>
       </c>
       <c r="T3">
-        <v>0.0997278289675102</v>
+        <v>0.09972782896266688</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -4707,22 +4707,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.6871444193498755</v>
+        <v>0.6871444193555964</v>
       </c>
       <c r="O4">
-        <v>0.8999999761544045</v>
+        <v>0.8999999761581394</v>
       </c>
       <c r="P4">
-        <v>0.6877025869993748</v>
+        <v>0.6877025870103592</v>
       </c>
       <c r="Q4">
-        <v>40.86384413760954</v>
+        <v>40.86384413666168</v>
       </c>
       <c r="R4">
-        <v>-89.99999999969845</v>
+        <v>-89.99999999999589</v>
       </c>
       <c r="S4">
-        <v>139.0824312334946</v>
+        <v>139.0824312333408</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -4769,22 +4769,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.6871444124240347</v>
+        <v>0.687144412430558</v>
       </c>
       <c r="O5">
-        <v>0.8999999761570947</v>
+        <v>0.8999999761581394</v>
       </c>
       <c r="P5">
-        <v>0.6877025833218861</v>
+        <v>0.6877025833366379</v>
       </c>
       <c r="Q5">
-        <v>40.86384436351678</v>
+        <v>40.8638443627645</v>
       </c>
       <c r="R5">
-        <v>-90.00000000035021</v>
+        <v>-89.99999999999589</v>
       </c>
       <c r="S5">
-        <v>139.082430693935</v>
+        <v>139.0824306946034</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -4903,22 +4903,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9498881090148401</v>
+        <v>0.9498881090148399</v>
       </c>
       <c r="O2">
-        <v>0.9499999880790728</v>
+        <v>0.949999988079071</v>
       </c>
       <c r="P2">
-        <v>0.9499700858544572</v>
+        <v>0.9499700858544576</v>
       </c>
       <c r="Q2">
         <v>29.99818695071847</v>
       </c>
       <c r="R2">
-        <v>-89.99999999999645</v>
+        <v>-89.99999999999635</v>
       </c>
       <c r="S2">
-        <v>149.9932497715756</v>
+        <v>149.9932497715758</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -4929,7 +4929,7 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>0.02438883360386583</v>
+        <v>0.02438883360420217</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -4938,7 +4938,7 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0.005632359942493873</v>
+        <v>0.005632359942571549</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -4947,43 +4947,43 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>3.933564400979036</v>
+        <v>3.933564400728284</v>
       </c>
       <c r="I3">
-        <v>1.380277273848993</v>
+        <v>1.38027727363123</v>
       </c>
       <c r="J3">
-        <v>0.9822689134123498</v>
+        <v>0.982268913409819</v>
       </c>
       <c r="K3">
-        <v>0.3474656433491256</v>
+        <v>0.347465643295257</v>
       </c>
       <c r="L3">
-        <v>0.9822689134193464</v>
+        <v>0.9822689134098265</v>
       </c>
       <c r="M3">
-        <v>0.3474656432902385</v>
+        <v>0.347465643295304</v>
       </c>
       <c r="N3">
-        <v>0.9102637354937271</v>
+        <v>0.9102637354936918</v>
       </c>
       <c r="O3">
-        <v>0.9499999880786464</v>
+        <v>0.949999988079071</v>
       </c>
       <c r="P3">
-        <v>0.8875538273736355</v>
+        <v>0.8875538273748504</v>
       </c>
       <c r="Q3">
-        <v>33.05430924256711</v>
+        <v>33.05430924257372</v>
       </c>
       <c r="R3">
-        <v>-90.00000000007398</v>
+        <v>-89.99999999999625</v>
       </c>
       <c r="S3">
-        <v>149.2716838231232</v>
+        <v>149.2716838231431</v>
       </c>
       <c r="T3">
-        <v>0.02438883360386583</v>
+        <v>0.02438883360420217</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -5027,22 +5027,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.9102637392883157</v>
+        <v>0.910263739288095</v>
       </c>
       <c r="O4">
-        <v>0.9499999880789385</v>
+        <v>0.949999988079071</v>
       </c>
       <c r="P4">
-        <v>0.8875538312976694</v>
+        <v>0.8875538312990119</v>
       </c>
       <c r="Q4">
-        <v>33.05430908484679</v>
+        <v>33.05430908485783</v>
       </c>
       <c r="R4">
-        <v>-90.00000000010357</v>
+        <v>-89.99999999999625</v>
       </c>
       <c r="S4">
-        <v>149.2716839713889</v>
+        <v>149.2716839714325</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -5089,22 +5089,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9102637377707754</v>
+        <v>0.9102637377703338</v>
       </c>
       <c r="O5">
-        <v>0.9499999880790508</v>
+        <v>0.949999988079071</v>
       </c>
       <c r="P5">
-        <v>0.8875538297275117</v>
+        <v>0.8875538297293475</v>
       </c>
       <c r="Q5">
-        <v>33.05430914792462</v>
+        <v>33.05430914794419</v>
       </c>
       <c r="R5">
-        <v>-90.0000000001576</v>
+        <v>-89.99999999999625</v>
       </c>
       <c r="S5">
-        <v>149.2716839120463</v>
+        <v>149.2716839121167</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -5223,22 +5223,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.8998995633246843</v>
+        <v>0.8998995633246877</v>
       </c>
       <c r="O2">
-        <v>0.8999999761581398</v>
+        <v>0.8999999761581415</v>
       </c>
       <c r="P2">
-        <v>0.8999731389721715</v>
+        <v>0.8999731389721763</v>
       </c>
       <c r="Q2">
-        <v>29.99828232124138</v>
+        <v>29.99828232124134</v>
       </c>
       <c r="R2">
-        <v>-89.99999999999648</v>
+        <v>-89.99999999999635</v>
       </c>
       <c r="S2">
-        <v>149.9936049936318</v>
+        <v>149.9936049936319</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -5249,7 +5249,7 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>0.02310539214610254</v>
+        <v>0.02310539214590443</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -5258,7 +5258,7 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0.005335961829625692</v>
+        <v>0.005335961829579941</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -5267,43 +5267,43 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>3.933554215957431</v>
+        <v>3.933554216279361</v>
       </c>
       <c r="I3">
-        <v>1.380177713378632</v>
+        <v>1.380177713395198</v>
       </c>
       <c r="J3">
-        <v>0.9822589630197631</v>
+        <v>0.9822589630275964</v>
       </c>
       <c r="K3">
-        <v>0.3473661396591991</v>
+        <v>0.3473661396185194</v>
       </c>
       <c r="L3">
-        <v>0.9822589630179832</v>
+        <v>0.9822589630275768</v>
       </c>
       <c r="M3">
-        <v>0.3473661396440931</v>
+        <v>0.3473661396185667</v>
       </c>
       <c r="N3">
-        <v>0.8623600932800334</v>
+        <v>0.8623600932803913</v>
       </c>
       <c r="O3">
-        <v>0.8999999761566391</v>
+        <v>0.8999999761581415</v>
       </c>
       <c r="P3">
-        <v>0.8408415018613912</v>
+        <v>0.8408415018635509</v>
       </c>
       <c r="Q3">
-        <v>33.05439499038046</v>
+        <v>33.05439499025354</v>
       </c>
       <c r="R3">
-        <v>-89.99999999996072</v>
+        <v>-89.99999999999626</v>
       </c>
       <c r="S3">
-        <v>149.2720275627785</v>
+        <v>149.2720275626354</v>
       </c>
       <c r="T3">
-        <v>0.02310539214610254</v>
+        <v>0.02310539214590443</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -5347,22 +5347,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8623600968749066</v>
+        <v>0.8623600968747794</v>
       </c>
       <c r="O4">
-        <v>0.8999999761569629</v>
+        <v>0.8999999761581415</v>
       </c>
       <c r="P4">
-        <v>0.8408415055801652</v>
+        <v>0.84084150558124</v>
       </c>
       <c r="Q4">
-        <v>33.05439483266308</v>
+        <v>33.05439483252454</v>
       </c>
       <c r="R4">
-        <v>-89.99999999989684</v>
+        <v>-89.99999999999625</v>
       </c>
       <c r="S4">
-        <v>149.2720277110921</v>
+        <v>149.2720277108982</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -5409,22 +5409,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8623600954370512</v>
+        <v>0.8623600954370242</v>
       </c>
       <c r="O5">
-        <v>0.8999999761570222</v>
+        <v>0.8999999761581415</v>
       </c>
       <c r="P5">
-        <v>0.8408415040914162</v>
+        <v>0.8408415040941642</v>
       </c>
       <c r="Q5">
-        <v>33.0543948957301</v>
+        <v>33.05439489561613</v>
       </c>
       <c r="R5">
-        <v>-90.00000000004432</v>
+        <v>-89.99999999999625</v>
       </c>
       <c r="S5">
-        <v>149.2720276516856</v>
+        <v>149.2720276515931</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -5543,22 +5543,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.050234052937969</v>
+        <v>1.050234052937961</v>
       </c>
       <c r="O2">
-        <v>1.048173411570587</v>
+        <v>1.048173411570604</v>
       </c>
       <c r="P2">
-        <v>1.048548232600595</v>
+        <v>1.048548232600658</v>
       </c>
       <c r="Q2">
-        <v>29.92175272018378</v>
+        <v>29.92175272018186</v>
       </c>
       <c r="R2">
-        <v>-90.11967249081376</v>
+        <v>-90.11967249081198</v>
       </c>
       <c r="S2">
-        <v>149.9985745740018</v>
+        <v>149.9985745740005</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -5572,58 +5572,58 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>0.3459755857683853</v>
+        <v>0.3459755857711127</v>
       </c>
       <c r="D3">
-        <v>0.3457034707011522</v>
+        <v>0.3457034707010911</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.07989964022116368</v>
+        <v>0.07989964022179356</v>
       </c>
       <c r="G3">
-        <v>0.07983679793730024</v>
+        <v>0.07983679793728612</v>
       </c>
       <c r="H3">
-        <v>2.048802864167397</v>
+        <v>2.048802864003135</v>
       </c>
       <c r="I3">
-        <v>1.383313298626652</v>
+        <v>1.383313298422268</v>
       </c>
       <c r="J3">
-        <v>0.5116671529599571</v>
+        <v>0.5116671529773194</v>
       </c>
       <c r="K3">
-        <v>0.3472468025996517</v>
+        <v>0.3472468026119639</v>
       </c>
       <c r="L3">
-        <v>0.5116671529366223</v>
+        <v>0.5116671529773235</v>
       </c>
       <c r="M3">
-        <v>0.3472468026066617</v>
+        <v>0.3472468026119976</v>
       </c>
       <c r="N3">
-        <v>0.8082392293762495</v>
+        <v>0.8082392293687279</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>0.8082392293733981</v>
+        <v>0.8082392293687033</v>
       </c>
       <c r="Q3">
-        <v>-0.01518447971802059</v>
+        <v>-0.01518448049999265</v>
       </c>
       <c r="R3">
         <v>0</v>
       </c>
       <c r="S3">
-        <v>179.9848155212159</v>
+        <v>179.9848155194906</v>
       </c>
       <c r="T3">
-        <v>0.1307791445982361</v>
+        <v>0.1307791446093346</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -5667,22 +5667,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8082392204479948</v>
+        <v>0.8082392204398072</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.808239245394656</v>
+        <v>0.8082392453957743</v>
       </c>
       <c r="Q4">
-        <v>-0.01518300026509494</v>
+        <v>-0.01518300111962987</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>179.9848143834887</v>
+        <v>179.9848143818178</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -5729,22 +5729,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8082392240176344</v>
+        <v>0.8082392240113753</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0.8082392389880783</v>
+        <v>0.8082392389849463</v>
       </c>
       <c r="Q5">
-        <v>-0.01518359206209005</v>
+        <v>-0.01518359287177051</v>
       </c>
       <c r="R5">
         <v>0</v>
       </c>
       <c r="S5">
-        <v>179.9848148389578</v>
+        <v>179.9848148368869</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -5863,22 +5863,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.100256815443219</v>
+        <v>1.100256815443185</v>
       </c>
       <c r="O2">
-        <v>1.097995431674414</v>
+        <v>1.09799543167444</v>
       </c>
       <c r="P2">
-        <v>1.098406899252564</v>
+        <v>1.098406899252609</v>
       </c>
       <c r="Q2">
-        <v>29.91803171923491</v>
+        <v>29.91803171923368</v>
       </c>
       <c r="R2">
-        <v>-90.12536079168059</v>
+        <v>-90.12536079167887</v>
       </c>
       <c r="S2">
-        <v>149.9985139394196</v>
+        <v>149.9985139394172</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -5892,58 +5892,58 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>0.3624257463715317</v>
+        <v>0.3624257463710422</v>
       </c>
       <c r="D3">
-        <v>0.3621317875585172</v>
+        <v>0.3621317875589192</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.08369864213874888</v>
+        <v>0.08369864213863584</v>
       </c>
       <c r="G3">
-        <v>0.08363075525780746</v>
+        <v>0.08363075525790029</v>
       </c>
       <c r="H3">
-        <v>2.048810925117779</v>
+        <v>2.04881092492271</v>
       </c>
       <c r="I3">
-        <v>1.383392955720942</v>
+        <v>1.383392955552335</v>
       </c>
       <c r="J3">
-        <v>0.5116751132619101</v>
+        <v>0.5116751132846749</v>
       </c>
       <c r="K3">
-        <v>0.347326405539256</v>
+        <v>0.3473264055688352</v>
       </c>
       <c r="L3">
-        <v>0.5116751132525802</v>
+        <v>0.5116751132846632</v>
       </c>
       <c r="M3">
-        <v>0.3473264055744294</v>
+        <v>0.3473264055688411</v>
       </c>
       <c r="N3">
-        <v>0.8467210279465175</v>
+        <v>0.8467210279325773</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>0.846721027946123</v>
+        <v>0.8467210279325691</v>
       </c>
       <c r="Q3">
-        <v>-0.01565922554282706</v>
+        <v>-0.0156592257915673</v>
       </c>
       <c r="R3">
         <v>0</v>
       </c>
       <c r="S3">
-        <v>179.9843407754452</v>
+        <v>179.9843407742001</v>
       </c>
       <c r="T3">
-        <v>0.1370029464496659</v>
+        <v>0.1370029464599702</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -5987,22 +5987,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8467210185931258</v>
+        <v>0.846721018578327</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.8467210447327723</v>
+        <v>0.8467210447230132</v>
       </c>
       <c r="Q4">
-        <v>-0.01565774605150279</v>
+        <v>-0.01565774638016302</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>179.9843396379124</v>
+        <v>179.9843396365551</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -6049,22 +6049,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8467210223326442</v>
+        <v>0.8467210223200269</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0.8467210380187524</v>
+        <v>0.8467210380068357</v>
       </c>
       <c r="Q5">
-        <v>-0.01565833786826649</v>
+        <v>-0.01565833814471741</v>
       </c>
       <c r="R5">
         <v>0</v>
       </c>
       <c r="S5">
-        <v>179.9843400932037</v>
+        <v>179.9843400916131</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -6183,19 +6183,19 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.049964148037376</v>
+        <v>1.049964148037377</v>
       </c>
       <c r="O2">
-        <v>1.049824400685044</v>
+        <v>1.049824400685046</v>
       </c>
       <c r="P2">
-        <v>1.049873815726581</v>
+        <v>1.049873815726591</v>
       </c>
       <c r="Q2">
-        <v>29.99320494129977</v>
+        <v>29.99320494129953</v>
       </c>
       <c r="R2">
-        <v>-90.00808470234212</v>
+        <v>-90.00808470234183</v>
       </c>
       <c r="S2">
         <v>149.9991649635709</v>
@@ -6212,58 +6212,58 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>0.03084976925745735</v>
+        <v>0.03084976925761263</v>
       </c>
       <c r="D3">
-        <v>0.03025270750124391</v>
+        <v>0.03025270750134595</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.007124449140254902</v>
+        <v>0.007124449140290762</v>
       </c>
       <c r="G3">
-        <v>0.006986563631931182</v>
+        <v>0.006986563631954748</v>
       </c>
       <c r="H3">
-        <v>2.048802864167397</v>
+        <v>2.048802864003135</v>
       </c>
       <c r="I3">
-        <v>1.383313298626652</v>
+        <v>1.383313298422268</v>
       </c>
       <c r="J3">
-        <v>0.5116671529599571</v>
+        <v>0.5116671529773194</v>
       </c>
       <c r="K3">
-        <v>0.3472468025996517</v>
+        <v>0.3472468026119639</v>
       </c>
       <c r="L3">
-        <v>0.5116671529366223</v>
+        <v>0.5116671529773235</v>
       </c>
       <c r="M3">
-        <v>0.3472468026066617</v>
+        <v>0.3472468026119976</v>
       </c>
       <c r="N3">
-        <v>1.006558191834797</v>
+        <v>1.006558191833886</v>
       </c>
       <c r="O3">
-        <v>0.9668366588187991</v>
+        <v>0.9668366588206877</v>
       </c>
       <c r="P3">
-        <v>1.016417179314449</v>
+        <v>1.016417179316686</v>
       </c>
       <c r="Q3">
-        <v>28.90317285760926</v>
+        <v>28.90317285753057</v>
       </c>
       <c r="R3">
-        <v>-89.13252169224673</v>
+        <v>-89.13252169220242</v>
       </c>
       <c r="S3">
-        <v>151.805341254004</v>
+        <v>151.805341253846</v>
       </c>
       <c r="T3">
-        <v>0.02725059742757435</v>
+        <v>0.02725059742806405</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -6307,22 +6307,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.006558192878358</v>
+        <v>1.006558192877255</v>
       </c>
       <c r="O4">
-        <v>0.9668366621171682</v>
+        <v>0.9668366621186248</v>
       </c>
       <c r="P4">
-        <v>1.016417181262188</v>
+        <v>1.016417181265221</v>
       </c>
       <c r="Q4">
-        <v>28.9031729563469</v>
+        <v>28.90317295625301</v>
       </c>
       <c r="R4">
-        <v>-89.13252160851521</v>
+        <v>-89.13252160841085</v>
       </c>
       <c r="S4">
-        <v>151.8053412326777</v>
+        <v>151.8053412325514</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -6369,22 +6369,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>1.006558192460617</v>
+        <v>1.006558192459908</v>
       </c>
       <c r="O5">
-        <v>0.9668366607970246</v>
+        <v>0.96683666079945</v>
       </c>
       <c r="P5">
-        <v>1.016417180483359</v>
+        <v>1.016417180485807</v>
       </c>
       <c r="Q5">
-        <v>28.90317291685507</v>
+        <v>28.90317291676403</v>
       </c>
       <c r="R5">
-        <v>-89.13252164194866</v>
+        <v>-89.13252164192748</v>
       </c>
       <c r="S5">
-        <v>151.8053412412615</v>
+        <v>151.8053412410692</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -6503,22 +6503,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.099960728154768</v>
+        <v>1.099960728154766</v>
       </c>
       <c r="O2">
-        <v>1.099807355906275</v>
+        <v>1.099807355906276</v>
       </c>
       <c r="P2">
-        <v>1.099861589226214</v>
+        <v>1.09986158922622</v>
       </c>
       <c r="Q2">
-        <v>29.99288142271792</v>
+        <v>29.9928814227177</v>
       </c>
       <c r="R2">
-        <v>-90.00846962073528</v>
+        <v>-90.00846962073501</v>
       </c>
       <c r="S2">
-        <v>149.9991252457517</v>
+        <v>149.9991252457516</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -6532,58 +6532,58 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>0.03231856841205823</v>
+        <v>0.03231856841214049</v>
       </c>
       <c r="D3">
-        <v>0.031693060150718</v>
+        <v>0.03169306015084904</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.00746365378022717</v>
+        <v>0.007463653780246165</v>
       </c>
       <c r="G3">
-        <v>0.007319198832848576</v>
+        <v>0.007319198832878839</v>
       </c>
       <c r="H3">
-        <v>2.048810925117779</v>
+        <v>2.04881092492271</v>
       </c>
       <c r="I3">
-        <v>1.383392955720942</v>
+        <v>1.383392955552335</v>
       </c>
       <c r="J3">
-        <v>0.5116751132619101</v>
+        <v>0.5116751132846749</v>
       </c>
       <c r="K3">
-        <v>0.347326405539256</v>
+        <v>0.3473264055688352</v>
       </c>
       <c r="L3">
-        <v>0.5116751132525802</v>
+        <v>0.5116751132846632</v>
       </c>
       <c r="M3">
-        <v>0.3473264055744294</v>
+        <v>0.3473264055688411</v>
       </c>
       <c r="N3">
-        <v>1.054488125406114</v>
+        <v>1.054488125404451</v>
       </c>
       <c r="O3">
-        <v>1.012868503185622</v>
+        <v>1.012868503187162</v>
       </c>
       <c r="P3">
-        <v>1.064812244096026</v>
+        <v>1.064812244096948</v>
       </c>
       <c r="Q3">
-        <v>28.90285935952483</v>
+        <v>28.90285935950884</v>
       </c>
       <c r="R3">
-        <v>-89.13290661057617</v>
+        <v>-89.13290661052247</v>
       </c>
       <c r="S3">
-        <v>151.8053072099275</v>
+        <v>151.8053072097962</v>
       </c>
       <c r="T3">
-        <v>0.0285480545538663</v>
+        <v>0.02854805455434508</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -6627,22 +6627,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.054488126499496</v>
+        <v>1.05448812649741</v>
       </c>
       <c r="O4">
-        <v>1.012868506640819</v>
+        <v>1.012868506642256</v>
       </c>
       <c r="P4">
-        <v>1.064812246137029</v>
+        <v>1.064812246138461</v>
       </c>
       <c r="Q4">
-        <v>28.90285945827612</v>
+        <v>28.90285945824466</v>
       </c>
       <c r="R4">
-        <v>-89.13290652679392</v>
+        <v>-89.13290652670456</v>
       </c>
       <c r="S4">
-        <v>151.8053071886477</v>
+        <v>151.8053071885102</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -6689,22 +6689,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>1.054488126061678</v>
+        <v>1.054488126060226</v>
       </c>
       <c r="O5">
-        <v>1.012868505258116</v>
+        <v>1.012868505260219</v>
       </c>
       <c r="P5">
-        <v>1.064812245320712</v>
+        <v>1.064812245321856</v>
       </c>
       <c r="Q5">
-        <v>28.90285941877868</v>
+        <v>28.90285941875034</v>
       </c>
       <c r="R5">
-        <v>-89.1329065602623</v>
+        <v>-89.1329065602317</v>
       </c>
       <c r="S5">
-        <v>151.8053071971902</v>
+        <v>151.8053071970246</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -6823,22 +6823,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9503581626365398</v>
+        <v>0.950358162636516</v>
       </c>
       <c r="O2">
-        <v>0.949263907864942</v>
+        <v>0.9492639078649423</v>
       </c>
       <c r="P2">
-        <v>0.9491512172441275</v>
+        <v>0.9491512172441227</v>
       </c>
       <c r="Q2">
-        <v>29.95136859201942</v>
+        <v>29.95136859201854</v>
       </c>
       <c r="R2">
-        <v>-90.0946189363426</v>
+        <v>-90.094618936343</v>
       </c>
       <c r="S2">
-        <v>149.9855933920535</v>
+        <v>149.9855933920516</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -6852,58 +6852,58 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>0.1857788844296786</v>
+        <v>0.1857788844337976</v>
       </c>
       <c r="D3">
-        <v>0.1856241055464245</v>
+        <v>0.1856241055465486</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.0429037962134057</v>
+        <v>0.04290379621435694</v>
       </c>
       <c r="G3">
-        <v>0.04286805156090842</v>
+        <v>0.04286805156093708</v>
       </c>
       <c r="H3">
-        <v>3.933564400950151</v>
+        <v>3.933564400728234</v>
       </c>
       <c r="I3">
-        <v>1.380277273778748</v>
+        <v>1.380277273631228</v>
       </c>
       <c r="J3">
-        <v>0.982268913438333</v>
+        <v>0.9822689134097025</v>
       </c>
       <c r="K3">
-        <v>0.3474656432863268</v>
+        <v>0.3474656432952729</v>
       </c>
       <c r="L3">
-        <v>0.9822689134386264</v>
+        <v>0.9822689134096926</v>
       </c>
       <c r="M3">
-        <v>0.3474656433264189</v>
+        <v>0.3474656432953018</v>
       </c>
       <c r="N3">
-        <v>0.7313310006237299</v>
+        <v>0.7313310006084235</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>0.7313310006254859</v>
+        <v>0.7313310006084299</v>
       </c>
       <c r="Q3">
-        <v>-0.01608258486532913</v>
+        <v>-0.01608258479789187</v>
       </c>
       <c r="R3">
         <v>0</v>
       </c>
       <c r="S3">
-        <v>179.9839174148756</v>
+        <v>179.9839174151944</v>
       </c>
       <c r="T3">
-        <v>0.07017346264459953</v>
+        <v>0.07017346264981066</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -6947,22 +6947,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.7313309954953042</v>
+        <v>0.7313309954794257</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.7313310180882647</v>
+        <v>0.7313310180678123</v>
       </c>
       <c r="Q4">
-        <v>-0.01607990107789777</v>
+        <v>-0.01607990112069938</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>179.9839150737142</v>
+        <v>179.9839150741862</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -7009,22 +7009,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.7313309975461124</v>
+        <v>0.7313309975310243</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0.7313310111037852</v>
+        <v>0.7313310110840596</v>
       </c>
       <c r="Q5">
-        <v>-0.01608097448670311</v>
+        <v>-0.0160809745915332</v>
       </c>
       <c r="R5">
         <v>0</v>
       </c>
       <c r="S5">
-        <v>179.983916010359</v>
+        <v>179.9839160105895</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -7268,22 +7268,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9003214985094843</v>
+        <v>0.9003214985094803</v>
       </c>
       <c r="O2">
-        <v>0.899339373239582</v>
+        <v>0.8993393732395846</v>
       </c>
       <c r="P2">
-        <v>0.8992381755753451</v>
+        <v>0.8992381755753385</v>
       </c>
       <c r="Q2">
-        <v>29.95392772300881</v>
+        <v>29.95392772300903</v>
       </c>
       <c r="R2">
-        <v>-90.08964264987566</v>
+        <v>-90.08964264987587</v>
       </c>
       <c r="S2">
-        <v>149.9863477144344</v>
+        <v>149.986347714434</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -7297,58 +7297,58 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>0.1760061738316752</v>
+        <v>0.1760061738339913</v>
       </c>
       <c r="D3">
-        <v>0.1758633179132011</v>
+        <v>0.1758633179147765</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.04064688534198727</v>
+        <v>0.04064688534252217</v>
       </c>
       <c r="G3">
-        <v>0.04061389418030113</v>
+        <v>0.04061389418066496</v>
       </c>
       <c r="H3">
-        <v>3.933554215993011</v>
+        <v>3.93355421627931</v>
       </c>
       <c r="I3">
-        <v>1.380177713283042</v>
+        <v>1.380177713395197</v>
       </c>
       <c r="J3">
-        <v>0.9822589630576509</v>
+        <v>0.9822589630274553</v>
       </c>
       <c r="K3">
-        <v>0.3473661396055267</v>
+        <v>0.3473661396185401</v>
       </c>
       <c r="L3">
-        <v>0.9822589630228384</v>
+        <v>0.9822589630274428</v>
       </c>
       <c r="M3">
-        <v>0.3473661396117605</v>
+        <v>0.3473661396185643</v>
       </c>
       <c r="N3">
-        <v>0.6928422324115322</v>
+        <v>0.6928422324108532</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>0.6928422324137804</v>
+        <v>0.6928422324108552</v>
       </c>
       <c r="Q3">
-        <v>-0.01566764946699842</v>
+        <v>-0.01566764921675467</v>
       </c>
       <c r="R3">
         <v>0</v>
       </c>
       <c r="S3">
-        <v>179.9843323504382</v>
+        <v>179.9843323507756</v>
       </c>
       <c r="T3">
-        <v>0.06648102571716608</v>
+        <v>0.06648102571494606</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -7392,22 +7392,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.6928422275524098</v>
+        <v>0.6928422275519983</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.6928422489506281</v>
+        <v>0.6928422489510784</v>
       </c>
       <c r="Q4">
-        <v>-0.01566496581391335</v>
+        <v>-0.01566496557836796</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>179.984330009336</v>
+        <v>179.9843300097328</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -7454,22 +7454,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.6928422294960122</v>
+        <v>0.6928422294955399</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0.6928422423404434</v>
+        <v>0.6928422423349895</v>
       </c>
       <c r="Q5">
-        <v>-0.01566603911164745</v>
+        <v>-0.01566603903368046</v>
       </c>
       <c r="R5">
         <v>0</v>
       </c>
       <c r="S5">
-        <v>179.9843309459008</v>
+        <v>179.9843309461499</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -7588,22 +7588,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9499744344990871</v>
+        <v>0.949974434499082</v>
       </c>
       <c r="O2">
-        <v>0.9498341377529774</v>
+        <v>0.949834137752982</v>
       </c>
       <c r="P2">
-        <v>0.9498810489682384</v>
+        <v>0.9498810489682352</v>
       </c>
       <c r="Q2">
-        <v>29.99245213177173</v>
+        <v>29.99245213177199</v>
       </c>
       <c r="R2">
-        <v>-90.00916683746635</v>
+        <v>-90.00916683746628</v>
       </c>
       <c r="S2">
-        <v>149.9989714861781</v>
+        <v>149.9989714861777</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -7617,58 +7617,58 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>0.0268903110173998</v>
+        <v>0.026890311017577</v>
       </c>
       <c r="D3">
-        <v>0.02529585666085731</v>
+        <v>0.02529585666088598</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.006210051414332391</v>
+        <v>0.006210051414373312</v>
       </c>
       <c r="G3">
-        <v>0.005841827948061281</v>
+        <v>0.005841827948067903</v>
       </c>
       <c r="H3">
-        <v>3.933564400950151</v>
+        <v>3.933564400728234</v>
       </c>
       <c r="I3">
-        <v>1.380277273778748</v>
+        <v>1.380277273631228</v>
       </c>
       <c r="J3">
-        <v>0.982268913438333</v>
+        <v>0.9822689134097025</v>
       </c>
       <c r="K3">
-        <v>0.3474656432863268</v>
+        <v>0.3474656432952729</v>
       </c>
       <c r="L3">
-        <v>0.9822689134386264</v>
+        <v>0.9822689134096926</v>
       </c>
       <c r="M3">
-        <v>0.3474656433264189</v>
+        <v>0.3474656432953018</v>
       </c>
       <c r="N3">
-        <v>0.8820887925191336</v>
+        <v>0.8820887925199997</v>
       </c>
       <c r="O3">
-        <v>0.8371884592972354</v>
+        <v>0.8371884592987457</v>
       </c>
       <c r="P3">
-        <v>0.9154331998861023</v>
+        <v>0.9154331998825589</v>
       </c>
       <c r="Q3">
-        <v>28.92650274056746</v>
+        <v>28.92650274080131</v>
       </c>
       <c r="R3">
-        <v>-86.79307942989828</v>
+        <v>-86.79307943004157</v>
       </c>
       <c r="S3">
-        <v>153.4469752304419</v>
+        <v>153.4469752304672</v>
       </c>
       <c r="T3">
-        <v>0.02197971479279758</v>
+        <v>0.02197971479326001</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -7712,22 +7712,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8820887966706115</v>
+        <v>0.8820887966711144</v>
       </c>
       <c r="O4">
-        <v>0.8371884680763559</v>
+        <v>0.8371884680777426</v>
       </c>
       <c r="P4">
-        <v>0.9154332034617011</v>
+        <v>0.9154332034574366</v>
       </c>
       <c r="Q4">
-        <v>28.92650292316413</v>
+        <v>28.92650292340137</v>
       </c>
       <c r="R4">
-        <v>-86.79307949442921</v>
+        <v>-86.79307949460488</v>
       </c>
       <c r="S4">
-        <v>153.4469750379367</v>
+        <v>153.4469750379372</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -7774,22 +7774,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8820887950096578</v>
+        <v>0.8820887950106686</v>
       </c>
       <c r="O5">
-        <v>0.8371884645646497</v>
+        <v>0.8371884645661439</v>
       </c>
       <c r="P5">
-        <v>0.915433202031522</v>
+        <v>0.9154332020274856</v>
       </c>
       <c r="Q5">
-        <v>28.92650285013812</v>
+        <v>28.92650285036135</v>
       </c>
       <c r="R5">
-        <v>-86.79307946858096</v>
+        <v>-86.79307946877957</v>
       </c>
       <c r="S5">
-        <v>153.4469751149465</v>
+        <v>153.4469751149491</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -7908,22 +7908,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.8999770420794047</v>
+        <v>0.8999770420794017</v>
       </c>
       <c r="O2">
-        <v>0.8998511235504446</v>
+        <v>0.8998511235504462</v>
       </c>
       <c r="P2">
-        <v>0.8998932265996008</v>
+        <v>0.899893226599597</v>
       </c>
       <c r="Q2">
-        <v>29.99284932528446</v>
+        <v>29.99284932528469</v>
       </c>
       <c r="R2">
-        <v>-90.00868445213437</v>
+        <v>-90.00868445213436</v>
       </c>
       <c r="S2">
-        <v>149.9990255662929</v>
+        <v>149.9990255662928</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -7937,58 +7937,58 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>0.02547524354365167</v>
+        <v>0.02547524354366063</v>
       </c>
       <c r="D3">
-        <v>0.02396471743389137</v>
+        <v>0.02396471743379126</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.005883255574706765</v>
+        <v>0.005883255574708835</v>
       </c>
       <c r="G3">
-        <v>0.005534414507073403</v>
+        <v>0.005534414507050282</v>
       </c>
       <c r="H3">
-        <v>3.933554215993011</v>
+        <v>3.93355421627931</v>
       </c>
       <c r="I3">
-        <v>1.380177713283042</v>
+        <v>1.380177713395197</v>
       </c>
       <c r="J3">
-        <v>0.9822589630576509</v>
+        <v>0.9822589630274553</v>
       </c>
       <c r="K3">
-        <v>0.3473661396055267</v>
+        <v>0.3473661396185401</v>
       </c>
       <c r="L3">
-        <v>0.9822589630228384</v>
+        <v>0.9822589630274428</v>
       </c>
       <c r="M3">
-        <v>0.3473661396117605</v>
+        <v>0.3473661396185643</v>
       </c>
       <c r="N3">
-        <v>0.8356638298181388</v>
+        <v>0.8356638298192888</v>
       </c>
       <c r="O3">
-        <v>0.7931331858678708</v>
+        <v>0.7931331858683009</v>
       </c>
       <c r="P3">
-        <v>0.8672577809518648</v>
+        <v>0.86725778095001</v>
       </c>
       <c r="Q3">
-        <v>28.92688267404945</v>
+        <v>28.92688267422177</v>
       </c>
       <c r="R3">
-        <v>-86.7925970447909</v>
+        <v>-86.79259704484494</v>
       </c>
       <c r="S3">
-        <v>153.4470258596719</v>
+        <v>153.4470258597794</v>
       </c>
       <c r="T3">
-        <v>0.02082302977283685</v>
+        <v>0.02082302977250878</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -8032,22 +8032,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.835663833750919</v>
+        <v>0.8356638337520207</v>
       </c>
       <c r="O4">
-        <v>0.7931331941843571</v>
+        <v>0.7931331941849045</v>
       </c>
       <c r="P4">
-        <v>0.8672577843376995</v>
+        <v>0.867257784336395</v>
       </c>
       <c r="Q4">
-        <v>28.92688285659513</v>
+        <v>28.92688285679296</v>
       </c>
       <c r="R4">
-        <v>-86.79259710947248</v>
+        <v>-86.79259710945777</v>
       </c>
       <c r="S4">
-        <v>153.4470256670953</v>
+        <v>153.4470256672386</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -8094,22 +8094,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8356638321776407</v>
+        <v>0.835663832178928</v>
       </c>
       <c r="O5">
-        <v>0.7931331908578483</v>
+        <v>0.7931331908582631</v>
       </c>
       <c r="P5">
-        <v>0.8672577829841629</v>
+        <v>0.8672577829818411</v>
       </c>
       <c r="Q5">
-        <v>28.92688278360279</v>
+        <v>28.92688278376449</v>
       </c>
       <c r="R5">
-        <v>-86.7925970835033</v>
+        <v>-86.79259708361263</v>
       </c>
       <c r="S5">
-        <v>153.44702574417</v>
+        <v>153.4470257442549</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -8850,22 +8850,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.050491592261001</v>
+        <v>1.050491592260995</v>
       </c>
       <c r="O2">
-        <v>1.048173411570598</v>
+        <v>1.048173411570605</v>
       </c>
       <c r="P2">
-        <v>1.048594781003152</v>
+        <v>1.048594781003185</v>
       </c>
       <c r="Q2">
         <v>29.92695589875414</v>
       </c>
       <c r="R2">
-        <v>-90.11967249081401</v>
+        <v>-90.11967249081198</v>
       </c>
       <c r="S2">
-        <v>150.013364054379</v>
+        <v>150.0133640543794</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -8876,55 +8876,55 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>0.3396015336196155</v>
+        <v>0.3396015336184986</v>
       </c>
       <c r="D3">
-        <v>0.3396015336196155</v>
+        <v>0.3396015336184985</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.07842761590966044</v>
+        <v>0.0784276159094025</v>
       </c>
       <c r="G3">
-        <v>0.07842761590966044</v>
+        <v>0.07842761590940248</v>
       </c>
       <c r="H3">
-        <v>2.048802864167397</v>
+        <v>2.048802864003135</v>
       </c>
       <c r="I3">
-        <v>1.383313298626652</v>
+        <v>1.383313298422268</v>
       </c>
       <c r="J3">
-        <v>0.5116671529599571</v>
+        <v>0.5116671529773194</v>
       </c>
       <c r="K3">
-        <v>0.3472468025996517</v>
+        <v>0.3472468026119639</v>
       </c>
       <c r="L3">
-        <v>0.5116671529366223</v>
+        <v>0.5116671529773235</v>
       </c>
       <c r="M3">
-        <v>0.3472468026066617</v>
+        <v>0.3472468026119976</v>
       </c>
       <c r="N3">
-        <v>0.9093266326803106</v>
+        <v>0.9093266326783842</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>0.9093266326736497</v>
+        <v>0.9093266326783628</v>
       </c>
       <c r="Q3">
-        <v>-4.778591225320545E-11</v>
+        <v>8.25205865442825E-13</v>
       </c>
       <c r="R3">
         <v>0</v>
       </c>
       <c r="S3">
-        <v>-179.9999999992685</v>
+        <v>179.9999999999919</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -8968,22 +8968,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.9093266202076929</v>
+        <v>0.9093266202052807</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.909326645144365</v>
+        <v>0.9093266451514664</v>
       </c>
       <c r="Q4">
-        <v>1.163178120337072E-06</v>
+        <v>1.163270335653725E-06</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>179.9999988374205</v>
+        <v>179.9999988367224</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -9027,22 +9027,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9093266251959025</v>
+        <v>0.9093266251945218</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0.9093266401541645</v>
+        <v>0.9093266401622254</v>
       </c>
       <c r="Q5">
-        <v>6.979014949868053E-07</v>
+        <v>6.979625413769643E-07</v>
       </c>
       <c r="R5">
         <v>0</v>
       </c>
       <c r="S5">
-        <v>179.9999993029566</v>
+        <v>179.9999993020302</v>
       </c>
     </row>
   </sheetData>
